--- a/SCIE용/산출물/엑셀/22_response_quality_eval_results.xlsx
+++ b/SCIE용/산출물/엑셀/22_response_quality_eval_results.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="응답 품질 평가" sheetId="1" r:id="rId1"/>
+    <sheet name="?? ?? ??" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -301,7 +301,7 @@
       </c>
       <c r="U2" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.52; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.52; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -404,7 +404,7 @@
       </c>
       <c r="U3" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.37; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.37; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="U4" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.66; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.66; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="U5" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.53; 일치키워드=고장; 텍스트순위=2; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.53; 일치키워드=고장; 텍스트순위=2; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="U6" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.43; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.43; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="U7" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.67; 일치키워드=고장; 텍스트순위=2; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.67; 일치키워드=고장; 텍스트순위=2; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="U8" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.53; 일치키워드=고장; 텍스트순위=2; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.53; 일치키워드=고장; 텍스트순위=2; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="U9" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.61; 일치키워드=고장; 텍스트순위=2; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.61; 일치키워드=고장; 텍스트순위=2; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="U10" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.55; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.55; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="U11" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.55; 일치키워드=누전차단기; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.55; 일치키워드=누전차단기; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="U12" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.77; 일치키워드=누전차단기,접지와; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.77; 일치키워드=누전차단기,접지와; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="U13" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.88; 일치키워드=접지와; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.88; 일치키워드=접지와; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="U14" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.56; 일치키워드=누전차단기; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.56; 일치키워드=누전차단기; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="U15" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.77; 일치키워드=누전차단기,접지와; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.77; 일치키워드=누전차단기,접지와; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="U16" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.88; 일치키워드=접지와; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.88; 일치키워드=접지와; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="U17" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.55; 일치키워드=누전차단기; 텍스트순위=1; 이미지순위=5</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.55; 일치키워드=누전차단기; 텍스트순위=1; 이미지순위=5</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="U18" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.77; 일치키워드=누전차단기,접지와; 텍스트순위=1; 이미지순위=5</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.77; 일치키워드=누전차단기,접지와; 텍스트순위=1; 이미지순위=5</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="U19" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.88; 일치키워드=접지와; 텍스트순위=1; 이미지순위=5</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.88; 일치키워드=접지와; 텍스트순위=1; 이미지순위=5</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="U20" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.66; 일치키워드=권장; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.66; 일치키워드=권장; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="U21" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.29; 의미유사도=0.78; 일치키워드=20nm,m8; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.29; 의미유사도=0.78; 일치키워드=20nm,m8; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="U22" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.29; 의미유사도=0.68; 일치키워드=20nm,m8; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.29; 의미유사도=0.68; 일치키워드=20nm,m8; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="U23" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.66; 일치키워드=권장; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.66; 일치키워드=권장; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="U24" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.63; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.63; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="U25" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.29; 의미유사도=0.68; 일치키워드=20nm,m8; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.29; 의미유사도=0.68; 일치키워드=20nm,m8; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="U26" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.66; 일치키워드=권장; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.66; 일치키워드=권장; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="U27" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.29; 의미유사도=0.78; 일치키워드=20nm,m8; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.29; 의미유사도=0.78; 일치키워드=20nm,m8; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="U28" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.29; 의미유사도=0.66; 일치키워드=20nm,m8; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.29; 의미유사도=0.66; 일치키워드=20nm,m8; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="U29" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.52; 일치키워드=단자블록의; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.52; 일치키워드=단자블록의; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="U30" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.61; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.61; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="U31" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.58; 일치키워드=tbsft; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.58; 일치키워드=tbsft; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="U32" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.59; 일치키워드=tbsft,단자블록의; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.59; 일치키워드=tbsft,단자블록의; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="U33" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.61; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.61; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="U34" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.59; 일치키워드=tbsft; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.59; 일치키워드=tbsft; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="U35" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.56; 일치키워드=단자블록의; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.56; 일치키워드=단자블록의; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="U36" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.61; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.61; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="U37" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.60; 일치키워드=tbsft; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.60; 일치키워드=tbsft; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="U38" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.56; 일치키워드=5번; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.56; 일치키워드=5번; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="U39" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.49; 일치키워드=5번; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.49; 일치키워드=5번; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="U40" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.51; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.51; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="U41" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.53; 일치키워드=5번; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.53; 일치키워드=5번; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="U42" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.49; 일치키워드=5번; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.49; 일치키워드=5번; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="U43" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.57; 일치키워드=5번; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.57; 일치키워드=5번; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="U44" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.54; 일치키워드=5번; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.54; 일치키워드=5번; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="U45" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.49; 일치키워드=5번; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.49; 일치키워드=5번; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="U46" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.38; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.38; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="U47" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.35; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.35; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="U48" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.88; 일치키워드=우측; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.88; 일치키워드=우측; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="U49" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.88; 일치키워드=우측; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.88; 일치키워드=우측; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="U50" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.35; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.35; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="U51" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.88; 일치키워드=우측; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.88; 일치키워드=우측; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="U52" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.88; 일치키워드=우측; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.88; 일치키워드=우측; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="U53" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.62; 일치키워드=우측; 텍스트순위=1; 이미지순위=6</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.62; 일치키워드=우측; 텍스트순위=1; 이미지순위=6</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="U54" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.88; 일치키워드=우측; 텍스트순위=1; 이미지순위=6</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.88; 일치키워드=우측; 텍스트순위=1; 이미지순위=6</t>
         </is>
       </c>
     </row>
@@ -5855,7 +5855,7 @@
       </c>
       <c r="U55" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.88; 일치키워드=우측; 텍스트순위=1; 이미지순위=6</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.88; 일치키워드=우측; 텍스트순위=1; 이미지순위=6</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="U56" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.52; 일치키워드=버튼; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.52; 일치키워드=버튼; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="U57" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.56; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.56; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="U58" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.64; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.64; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="U59" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.51; 일치키워드=; 텍스트순위=1; 이미지순위=10</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.51; 일치키워드=; 텍스트순위=1; 이미지순위=10</t>
         </is>
       </c>
     </row>
@@ -6378,7 +6378,7 @@
       </c>
       <c r="U60" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.56; 일치키워드=; 텍스트순위=1; 이미지순위=10</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.56; 일치키워드=; 텍스트순위=1; 이미지순위=10</t>
         </is>
       </c>
     </row>
@@ -6485,7 +6485,7 @@
       </c>
       <c r="U61" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.64; 일치키워드=; 텍스트순위=1; 이미지순위=10</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.64; 일치키워드=; 텍스트순위=1; 이미지순위=10</t>
         </is>
       </c>
     </row>
@@ -6592,7 +6592,7 @@
       </c>
       <c r="U62" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.48; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.48; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
       </c>
       <c r="U63" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.47; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.47; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="U64" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.64; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.64; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -6916,7 +6916,7 @@
       </c>
       <c r="U65" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.17; 의미유사도=0.42; 일치키워드=연결; 텍스트순위=2; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.17; 의미유사도=0.42; 일치키워드=연결; 텍스트순위=2; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="U66" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.53; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.53; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -7123,7 +7123,7 @@
       </c>
       <c r="U67" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.45; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.45; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="U68" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.17; 의미유사도=0.41; 일치키워드=연결; 텍스트순위=2; 이미지순위=4</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.17; 의미유사도=0.41; 일치키워드=연결; 텍스트순위=2; 이미지순위=4</t>
         </is>
       </c>
     </row>
@@ -7343,7 +7343,7 @@
       </c>
       <c r="U69" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.53; 일치키워드=; 텍스트순위=2; 이미지순위=4</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.53; 일치키워드=; 텍스트순위=2; 이미지순위=4</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="U70" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.48; 일치키워드=; 텍스트순위=2; 이미지순위=4</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.48; 일치키워드=; 텍스트순위=2; 이미지순위=4</t>
         </is>
       </c>
     </row>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="U71" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.17; 의미유사도=0.44; 일치키워드=연결; 텍스트순위=1; 이미지순위=4</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.17; 의미유사도=0.44; 일치키워드=연결; 텍스트순위=1; 이미지순위=4</t>
         </is>
       </c>
     </row>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="U72" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.55; 일치키워드=; 텍스트순위=1; 이미지순위=4</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.55; 일치키워드=; 텍스트순위=1; 이미지순위=4</t>
         </is>
       </c>
     </row>
@@ -7778,7 +7778,7 @@
       </c>
       <c r="U73" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.17; 의미유사도=0.49; 일치키워드=24v; 텍스트순위=1; 이미지순위=4</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.17; 의미유사도=0.49; 일치키워드=24v; 텍스트순위=1; 이미지순위=4</t>
         </is>
       </c>
     </row>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="U74" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.44; 일치키워드=보호; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.44; 일치키워드=보호; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="U75" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.51; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.51; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -8088,7 +8088,7 @@
       </c>
       <c r="U76" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.48; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.48; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="U77" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.44; 일치키워드=보호; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.44; 일치키워드=보호; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -8304,7 +8304,7 @@
       </c>
       <c r="U78" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.40; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.40; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="U79" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.47; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.47; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="U80" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.43; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.43; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="U81" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.38; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.38; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="U82" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.43; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.43; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -8845,7 +8845,7 @@
       </c>
       <c r="U83" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.44; 일치키워드=; 텍스트순위=8; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.44; 일치키워드=; 텍스트순위=8; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -8948,7 +8948,7 @@
       </c>
       <c r="U84" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.46; 일치키워드=; 텍스트순위=8; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.46; 일치키워드=; 텍스트순위=8; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="U85" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.40; 일치키워드=; 텍스트순위=8; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.40; 일치키워드=; 텍스트순위=8; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -9159,7 +9159,7 @@
       </c>
       <c r="U86" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.43; 일치키워드=; 텍스트순위=8; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.43; 일치키워드=; 텍스트순위=8; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="U87" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.46; 일치키워드=; 텍스트순위=8; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.46; 일치키워드=; 텍스트순위=8; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="U88" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.45; 일치키워드=; 텍스트순위=8; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.45; 일치키워드=; 텍스트순위=8; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="U89" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.45; 일치키워드=; 텍스트순위=8; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.45; 일치키워드=; 텍스트순위=8; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -9575,7 +9575,7 @@
       </c>
       <c r="U90" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.44; 일치키워드=; 텍스트순위=8; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.44; 일치키워드=; 텍스트순위=8; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="U91" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.42; 일치키워드=; 텍스트순위=8; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.42; 일치키워드=; 텍스트순위=8; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="U92" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.57; 일치키워드=회전과; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.57; 일치키워드=회전과; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="U93" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.40; 의미유사도=0.73; 일치키워드=회전과,회전으로; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.40; 의미유사도=0.73; 일치키워드=회전과,회전으로; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="U94" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.40; 의미유사도=0.73; 일치키워드=회전과,회전으로; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.40; 의미유사도=0.73; 일치키워드=회전과,회전으로; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="U95" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.69; 일치키워드=z축; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.69; 일치키워드=z축; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -10200,7 +10200,7 @@
       </c>
       <c r="U96" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.40; 의미유사도=0.73; 일치키워드=회전과,회전으로; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.40; 의미유사도=0.73; 일치키워드=회전과,회전으로; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -10304,7 +10304,7 @@
       </c>
       <c r="U97" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.40; 의미유사도=0.73; 일치키워드=회전과,회전으로; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.40; 의미유사도=0.73; 일치키워드=회전과,회전으로; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -10407,7 +10407,7 @@
       </c>
       <c r="U98" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.65; 일치키워드=z축; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.65; 일치키워드=z축; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="U99" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.40; 의미유사도=0.73; 일치키워드=회전과,회전으로; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.40; 의미유사도=0.73; 일치키워드=회전과,회전으로; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="U100" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.40; 의미유사도=0.73; 일치키워드=회전과,회전으로; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.40; 의미유사도=0.73; 일치키워드=회전과,회전으로; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -10722,7 +10722,7 @@
       </c>
       <c r="U101" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.53; 일치키워드=backdrive; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.53; 일치키워드=backdrive; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -10826,7 +10826,7 @@
       </c>
       <c r="U102" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.57; 일치키워드=backdrive; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.57; 일치키워드=backdrive; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -10931,7 +10931,7 @@
       </c>
       <c r="U103" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.54; 일치키워드=backdrive; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.54; 일치키워드=backdrive; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -11043,7 +11043,7 @@
       </c>
       <c r="U104" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.51; 일치키워드=backdrive; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.51; 일치키워드=backdrive; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="U105" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.57; 일치키워드=backdrive; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.57; 일치키워드=backdrive; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -11257,7 +11257,7 @@
       </c>
       <c r="U106" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.41; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.41; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -11368,7 +11368,7 @@
       </c>
       <c r="U107" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.52; 일치키워드=backdrive; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.52; 일치키워드=backdrive; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -11476,7 +11476,7 @@
       </c>
       <c r="U108" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.61; 일치키워드=backdrive; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.61; 일치키워드=backdrive; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -11583,7 +11583,7 @@
       </c>
       <c r="U109" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.41; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.41; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -11686,7 +11686,7 @@
       </c>
       <c r="U110" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.73; 일치키워드=길게,버튼을,이상,전원; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.73; 일치키워드=길게,버튼을,이상,전원; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -11789,7 +11789,7 @@
       </c>
       <c r="U111" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.76; 일치키워드=4초,길게,버튼을,이상,전원; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.76; 일치키워드=4초,길게,버튼을,이상,전원; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
       </c>
       <c r="U112" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.76; 일치키워드=길게,버튼을,이상,전원; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.76; 일치키워드=길게,버튼을,이상,전원; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="U113" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.73; 일치키워드=길게,버튼을,이상,전원; 텍스트순위=1; 이미지순위=5</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.73; 일치키워드=길게,버튼을,이상,전원; 텍스트순위=1; 이미지순위=5</t>
         </is>
       </c>
     </row>
@@ -12106,7 +12106,7 @@
       </c>
       <c r="U114" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.76; 일치키워드=4초,길게,버튼을,이상,전원; 텍스트순위=1; 이미지순위=5</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.76; 일치키워드=4초,길게,버튼을,이상,전원; 텍스트순위=1; 이미지순위=5</t>
         </is>
       </c>
     </row>
@@ -12213,7 +12213,7 @@
       </c>
       <c r="U115" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.76; 일치키워드=길게,버튼을,이상,전원; 텍스트순위=1; 이미지순위=5</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.76; 일치키워드=길게,버튼을,이상,전원; 텍스트순위=1; 이미지순위=5</t>
         </is>
       </c>
     </row>
@@ -12321,7 +12321,7 @@
       </c>
       <c r="U116" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.67; 일치키워드=길게,버튼을,이상,전원; 텍스트순위=1; 이미지순위=8</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.67; 일치키워드=길게,버튼을,이상,전원; 텍스트순위=1; 이미지순위=8</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="U117" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.79; 일치키워드=4초,길게,버튼을,이상,전원; 텍스트순위=1; 이미지순위=8</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.79; 일치키워드=4초,길게,버튼을,이상,전원; 텍스트순위=1; 이미지순위=8</t>
         </is>
       </c>
     </row>
@@ -12536,7 +12536,7 @@
       </c>
       <c r="U118" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.69; 일치키워드=길게,버튼을,이상,전원; 텍스트순위=1; 이미지순위=8</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.69; 일치키워드=길게,버튼을,이상,전원; 텍스트순위=1; 이미지순위=8</t>
         </is>
       </c>
     </row>
@@ -12645,7 +12645,7 @@
       </c>
       <c r="U119" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.57; 일치키워드=에러,조인트; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.57; 일치키워드=에러,조인트; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12750,7 @@
       </c>
       <c r="U120" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.55; 일치키워드=에러,조인트; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.55; 일치키워드=에러,조인트; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -12853,7 +12853,7 @@
       </c>
       <c r="U121" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.48; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.48; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -12966,7 +12966,7 @@
       </c>
       <c r="U122" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.65; 일치키워드=각도,속력,에러,조인트; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.65; 일치키워드=각도,속력,에러,조인트; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -13073,7 +13073,7 @@
       </c>
       <c r="U123" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.12; 의미유사도=0.57; 일치키워드=조인트; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.12; 의미유사도=0.57; 일치키워드=조인트; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -13180,7 +13180,7 @@
       </c>
       <c r="U124" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.47; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.47; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -13291,7 +13291,7 @@
       </c>
       <c r="U125" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.62; 일치키워드=각도,조인트; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.62; 일치키워드=각도,조인트; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -13398,7 +13398,7 @@
       </c>
       <c r="U126" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.45; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.45; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -13505,7 +13505,7 @@
       </c>
       <c r="U127" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.73; 일치키워드=각도,속력,제한,조인트; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.73; 일치키워드=각도,속력,제한,조인트; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -13611,7 +13611,7 @@
       </c>
       <c r="U128" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.47; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.47; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -13714,7 +13714,7 @@
       </c>
       <c r="U129" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.49; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.49; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -13817,7 +13817,7 @@
       </c>
       <c r="U130" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.53; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.53; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -13925,7 +13925,7 @@
       </c>
       <c r="U131" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.48; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.48; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -14028,7 +14028,7 @@
       </c>
       <c r="U132" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.46; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.46; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="U133" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.53; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.53; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -14238,7 +14238,7 @@
       </c>
       <c r="U134" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.47; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.47; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -14341,7 +14341,7 @@
       </c>
       <c r="U135" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.49; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.49; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -14444,7 +14444,7 @@
       </c>
       <c r="U136" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.52; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.52; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="U137" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.49; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.49; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -14650,7 +14650,7 @@
       </c>
       <c r="U138" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.82; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.82; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -14753,7 +14753,7 @@
       </c>
       <c r="U139" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.59; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.59; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -14860,7 +14860,7 @@
       </c>
       <c r="U140" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.49; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.49; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -14967,7 +14967,7 @@
       </c>
       <c r="U141" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.82; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.82; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -15074,7 +15074,7 @@
       </c>
       <c r="U142" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.59; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.59; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -15181,7 +15181,7 @@
       </c>
       <c r="U143" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.49; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.49; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -15288,7 +15288,7 @@
       </c>
       <c r="U144" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.82; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.82; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -15395,7 +15395,7 @@
       </c>
       <c r="U145" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.59; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.59; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -15507,7 +15507,7 @@
       </c>
       <c r="U146" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.54; 일치키워드=485,rs; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.54; 일치키워드=485,rs; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -15610,7 +15610,7 @@
       </c>
       <c r="U147" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.72; 일치키워드=485,6번,rs; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.72; 일치키워드=485,6번,rs; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -15716,7 +15716,7 @@
       </c>
       <c r="U148" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.55; 일치키워드=485,rs; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.55; 일치키워드=485,rs; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -15823,7 +15823,7 @@
       </c>
       <c r="U149" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.51; 일치키워드=485,rs; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.51; 일치키워드=485,rs; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -15930,7 +15930,7 @@
       </c>
       <c r="U150" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.61; 일치키워드=6번; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.61; 일치키워드=6번; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="U151" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.56; 일치키워드=485,rs; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.56; 일치키워드=485,rs; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -16149,7 +16149,7 @@
       </c>
       <c r="U152" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.00; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.00; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -16256,7 +16256,7 @@
       </c>
       <c r="U153" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.53; 일치키워드=4번; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.53; 일치키워드=4번; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -16363,7 +16363,7 @@
       </c>
       <c r="U154" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.57; 일치키워드=485,rs; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.57; 일치키워드=485,rs; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -16466,7 +16466,7 @@
       </c>
       <c r="U155" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.74; 일치키워드=구역,방지,협착; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.74; 일치키워드=구역,방지,협착; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="U156" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.94; 일치키워드=crushing,prevention,zone,구역,방지,협착; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.94; 일치키워드=crushing,prevention,zone,구역,방지,협착; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -16673,7 +16673,7 @@
       </c>
       <c r="U157" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.74; 일치키워드=crushing,prevention,zone,구역,방지,협착; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.74; 일치키워드=crushing,prevention,zone,구역,방지,협착; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -16780,7 +16780,7 @@
       </c>
       <c r="U158" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.74; 일치키워드=구역,방지,협착; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.74; 일치키워드=구역,방지,협착; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="U159" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.94; 일치키워드=crushing,prevention,zone,구역,방지,협착; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.94; 일치키워드=crushing,prevention,zone,구역,방지,협착; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -16996,7 +16996,7 @@
       </c>
       <c r="U160" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.79; 일치키워드=crushing,prevention,zone,구역,방지,협착; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.79; 일치키워드=crushing,prevention,zone,구역,방지,협착; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -17103,7 +17103,7 @@
       </c>
       <c r="U161" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.67; 일치키워드=구역,방지,협착; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.67; 일치키워드=구역,방지,협착; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="U162" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.81; 일치키워드=crushing,prevention,zone,구역,방지,협착; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.81; 일치키워드=crushing,prevention,zone,구역,방지,협착; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -17318,7 +17318,7 @@
       </c>
       <c r="U163" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.83; 일치키워드=crushing,prevention,zone,구역,방지,협착; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.83; 일치키워드=crushing,prevention,zone,구역,방지,협착; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -17422,7 +17422,7 @@
       </c>
       <c r="U164" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.47; 일치키워드=모션; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.47; 일치키워드=모션; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -17525,7 +17525,7 @@
       </c>
       <c r="U165" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.81; 일치키워드=태스크; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.81; 일치키워드=태스크; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -17628,7 +17628,7 @@
       </c>
       <c r="U166" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.54; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.54; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -17733,7 +17733,7 @@
       </c>
       <c r="U167" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.47; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.47; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -17836,7 +17836,7 @@
       </c>
       <c r="U168" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.81; 일치키워드=태스크; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.81; 일치키워드=태스크; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -17939,7 +17939,7 @@
       </c>
       <c r="U169" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.54; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.54; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -18046,7 +18046,7 @@
       </c>
       <c r="U170" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.62; 일치키워드=모션,태스크; 텍스트순위=1; 이미지순위=8</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.62; 일치키워드=모션,태스크; 텍스트순위=1; 이미지순위=8</t>
         </is>
       </c>
     </row>
@@ -18153,7 +18153,7 @@
       </c>
       <c r="U171" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.82; 일치키워드=모션,태스크; 텍스트순위=1; 이미지순위=8</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.82; 일치키워드=모션,태스크; 텍스트순위=1; 이미지순위=8</t>
         </is>
       </c>
     </row>
@@ -18260,7 +18260,7 @@
       </c>
       <c r="U172" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.59; 일치키워드=; 텍스트순위=1; 이미지순위=8</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.59; 일치키워드=; 텍스트순위=1; 이미지순위=8</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="U173" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.54; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.54; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -18466,7 +18466,7 @@
       </c>
       <c r="U174" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.44; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.44; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -18569,7 +18569,7 @@
       </c>
       <c r="U175" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.54; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.54; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -18676,7 +18676,7 @@
       </c>
       <c r="U176" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.53; 일치키워드=; 텍스트순위=2; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.53; 일치키워드=; 텍스트순위=2; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -18783,7 +18783,7 @@
       </c>
       <c r="U177" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.58; 일치키워드=; 텍스트순위=2; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.58; 일치키워드=; 텍스트순위=2; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -18891,7 +18891,7 @@
       </c>
       <c r="U178" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.52; 일치키워드=; 텍스트순위=2; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.52; 일치키워드=; 텍스트순위=2; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="U179" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.55; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.55; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -19105,7 +19105,7 @@
       </c>
       <c r="U180" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.56; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.56; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -19212,7 +19212,7 @@
       </c>
       <c r="U181" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.57; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.57; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -19315,7 +19315,7 @@
       </c>
       <c r="U182" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.46; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.46; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -19418,7 +19418,7 @@
       </c>
       <c r="U183" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.90; 일치키워드=기울어진,다면상자,원기둥,직육면체; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.90; 일치키워드=기울어진,다면상자,원기둥,직육면체; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="U184" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.55; 일치키워드=기울어진,다면상자,원기둥,직육면체; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.55; 일치키워드=기울어진,다면상자,원기둥,직육면체; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -19633,7 +19633,7 @@
       </c>
       <c r="U185" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.46; 일치키워드=; 텍스트순위=1; 이미지순위=4</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.46; 일치키워드=; 텍스트순위=1; 이미지순위=4</t>
         </is>
       </c>
     </row>
@@ -19740,7 +19740,7 @@
       </c>
       <c r="U186" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.90; 일치키워드=기울어진,다면상자,원기둥,직육면체; 텍스트순위=1; 이미지순위=4</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.90; 일치키워드=기울어진,다면상자,원기둥,직육면체; 텍스트순위=1; 이미지순위=4</t>
         </is>
       </c>
     </row>
@@ -19853,7 +19853,7 @@
       </c>
       <c r="U187" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.54; 일치키워드=기울어진,다면상자,원기둥,직육면체; 텍스트순위=1; 이미지순위=4</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.54; 일치키워드=기울어진,다면상자,원기둥,직육면체; 텍스트순위=1; 이미지순위=4</t>
         </is>
       </c>
     </row>
@@ -19960,7 +19960,7 @@
       </c>
       <c r="U188" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.46; 일치키워드=; 텍스트순위=1; 이미지순위=4</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.46; 일치키워드=; 텍스트순위=1; 이미지순위=4</t>
         </is>
       </c>
     </row>
@@ -20067,7 +20067,7 @@
       </c>
       <c r="U189" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.90; 일치키워드=기울어진,다면상자,원기둥,직육면체; 텍스트순위=1; 이미지순위=4</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.90; 일치키워드=기울어진,다면상자,원기둥,직육면체; 텍스트순위=1; 이미지순위=4</t>
         </is>
       </c>
     </row>
@@ -20179,7 +20179,7 @@
       </c>
       <c r="U190" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.56; 일치키워드=기울어진,다면상자,원기둥,직육면체; 텍스트순위=1; 이미지순위=4</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.56; 일치키워드=기울어진,다면상자,원기둥,직육면체; 텍스트순위=1; 이미지순위=4</t>
         </is>
       </c>
     </row>
@@ -20282,7 +20282,7 @@
       </c>
       <c r="U191" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.30; 일치키워드=; 텍스트순위=10; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.30; 일치키워드=; 텍스트순위=10; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -20385,7 +20385,7 @@
       </c>
       <c r="U192" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.32; 일치키워드=; 텍스트순위=10; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.32; 일치키워드=; 텍스트순위=10; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -20488,7 +20488,7 @@
       </c>
       <c r="U193" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.41; 일치키워드=; 텍스트순위=10; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.41; 일치키워드=; 텍스트순위=10; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -20591,7 +20591,7 @@
       </c>
       <c r="U194" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.30; 일치키워드=; 텍스트순위=10; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.30; 일치키워드=; 텍스트순위=10; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -20694,7 +20694,7 @@
       </c>
       <c r="U195" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.30; 일치키워드=; 텍스트순위=10; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.30; 일치키워드=; 텍스트순위=10; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -20797,7 +20797,7 @@
       </c>
       <c r="U196" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.38; 일치키워드=; 텍스트순위=10; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.38; 일치키워드=; 텍스트순위=10; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -20900,7 +20900,7 @@
       </c>
       <c r="U197" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.36; 일치키워드=; 텍스트순위=10; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.36; 일치키워드=; 텍스트순위=10; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -21003,7 +21003,7 @@
       </c>
       <c r="U198" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.32; 일치키워드=; 텍스트순위=10; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.32; 일치키워드=; 텍스트순위=10; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -21106,7 +21106,7 @@
       </c>
       <c r="U199" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.42; 일치키워드=; 텍스트순위=10; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.42; 일치키워드=; 텍스트순위=10; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="U200" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.45; 일치키워드=시간; 텍스트순위=4; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.45; 일치키워드=시간; 텍스트순위=4; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -21313,7 +21313,7 @@
       </c>
       <c r="U201" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.47; 일치키워드=시간; 텍스트순위=4; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.47; 일치키워드=시간; 텍스트순위=4; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -21416,7 +21416,7 @@
       </c>
       <c r="U202" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.51; 일치키워드=시간; 텍스트순위=4; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.51; 일치키워드=시간; 텍스트순위=4; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -21519,7 +21519,7 @@
       </c>
       <c r="U203" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.45; 일치키워드=시간; 텍스트순위=4; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.45; 일치키워드=시간; 텍스트순위=4; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -21622,7 +21622,7 @@
       </c>
       <c r="U204" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.49; 일치키워드=시간; 텍스트순위=4; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.49; 일치키워드=시간; 텍스트순위=4; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -21725,7 +21725,7 @@
       </c>
       <c r="U205" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.56; 일치키워드=시간; 텍스트순위=4; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.56; 일치키워드=시간; 텍스트순위=4; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="U206" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.45; 일치키워드=시간; 텍스트순위=4; 이미지순위=5</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.45; 일치키워드=시간; 텍스트순위=4; 이미지순위=5</t>
         </is>
       </c>
     </row>
@@ -21939,7 +21939,7 @@
       </c>
       <c r="U207" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.45; 일치키워드=시간; 텍스트순위=4; 이미지순위=5</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.45; 일치키워드=시간; 텍스트순위=4; 이미지순위=5</t>
         </is>
       </c>
     </row>
@@ -22046,7 +22046,7 @@
       </c>
       <c r="U208" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.51; 일치키워드=시간; 텍스트순위=4; 이미지순위=5</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.51; 일치키워드=시간; 텍스트순위=4; 이미지순위=5</t>
         </is>
       </c>
     </row>
@@ -22149,7 +22149,7 @@
       </c>
       <c r="U209" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.52; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.52; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -22252,7 +22252,7 @@
       </c>
       <c r="U210" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.58; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.58; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -22355,7 +22355,7 @@
       </c>
       <c r="U211" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.60; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.60; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -22458,7 +22458,7 @@
       </c>
       <c r="U212" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.51; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.51; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -22561,7 +22561,7 @@
       </c>
       <c r="U213" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.58; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.58; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -22664,7 +22664,7 @@
       </c>
       <c r="U214" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.60; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.60; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -22771,7 +22771,7 @@
       </c>
       <c r="U215" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.51; 일치키워드=; 텍스트순위=2; 이미지순위=7</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.51; 일치키워드=; 텍스트순위=2; 이미지순위=7</t>
         </is>
       </c>
     </row>
@@ -22878,7 +22878,7 @@
       </c>
       <c r="U216" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.80; 일치키워드=; 텍스트순위=2; 이미지순위=7</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.80; 일치키워드=; 텍스트순위=2; 이미지순위=7</t>
         </is>
       </c>
     </row>
@@ -22985,7 +22985,7 @@
       </c>
       <c r="U217" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.72; 일치키워드=; 텍스트순위=2; 이미지순위=7</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.72; 일치키워드=; 텍스트순위=2; 이미지순위=7</t>
         </is>
       </c>
     </row>
@@ -23088,7 +23088,7 @@
       </c>
       <c r="U218" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.48; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.48; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -23191,7 +23191,7 @@
       </c>
       <c r="U219" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.84; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.84; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -23294,7 +23294,7 @@
       </c>
       <c r="U220" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.52; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.52; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -23397,7 +23397,7 @@
       </c>
       <c r="U221" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.49; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.49; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -23500,7 +23500,7 @@
       </c>
       <c r="U222" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.58; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.58; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -23603,7 +23603,7 @@
       </c>
       <c r="U223" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.59; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.59; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -23706,7 +23706,7 @@
       </c>
       <c r="U224" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.51; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.51; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -23809,7 +23809,7 @@
       </c>
       <c r="U225" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.58; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.58; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -23912,7 +23912,7 @@
       </c>
       <c r="U226" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.52; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.52; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -24015,7 +24015,7 @@
       </c>
       <c r="U227" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.82; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.82; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -24118,7 +24118,7 @@
       </c>
       <c r="U228" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.75; 일치키워드=dm; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.75; 일치키워드=dm; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -24221,7 +24221,7 @@
       </c>
       <c r="U229" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.75; 일치키워드=dm; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.75; 일치키워드=dm; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -24328,7 +24328,7 @@
       </c>
       <c r="U230" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.75; 일치키워드=; 텍스트순위=1; 이미지순위=3</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.75; 일치키워드=; 텍스트순위=1; 이미지순위=3</t>
         </is>
       </c>
     </row>
@@ -24435,7 +24435,7 @@
       </c>
       <c r="U231" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.75; 일치키워드=dm; 텍스트순위=1; 이미지순위=3</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.75; 일치키워드=dm; 텍스트순위=1; 이미지순위=3</t>
         </is>
       </c>
     </row>
@@ -24542,7 +24542,7 @@
       </c>
       <c r="U232" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.75; 일치키워드=dm; 텍스트순위=1; 이미지순위=3</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.75; 일치키워드=dm; 텍스트순위=1; 이미지순위=3</t>
         </is>
       </c>
     </row>
@@ -24649,7 +24649,7 @@
       </c>
       <c r="U233" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.42; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.42; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -24756,7 +24756,7 @@
       </c>
       <c r="U234" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.75; 일치키워드=dm; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.75; 일치키워드=dm; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -24863,7 +24863,7 @@
       </c>
       <c r="U235" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.75; 일치키워드=dm; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.75; 일치키워드=dm; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -24966,7 +24966,7 @@
       </c>
       <c r="U236" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.57; 의미유사도=0.69; 일치키워드=아이템,워크셀,태스크,파일; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.57; 의미유사도=0.69; 일치키워드=아이템,워크셀,태스크,파일; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -25069,7 +25069,7 @@
       </c>
       <c r="U237" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.57; 의미유사도=0.82; 일치키워드=아이템,워크셀,태스크,파일; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.57; 의미유사도=0.82; 일치키워드=아이템,워크셀,태스크,파일; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -25172,7 +25172,7 @@
       </c>
       <c r="U238" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.86; 의미유사도=0.69; 일치키워드=데이터,베이스,아이템,워크셀,태스크,파일; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.86; 의미유사도=0.69; 일치키워드=데이터,베이스,아이템,워크셀,태스크,파일; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -25284,7 +25284,7 @@
       </c>
       <c r="U239" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.57; 의미유사도=0.59; 일치키워드=아이템,워크셀,태스크,파일; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.57; 의미유사도=0.59; 일치키워드=아이템,워크셀,태스크,파일; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -25391,7 +25391,7 @@
       </c>
       <c r="U240" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.57; 의미유사도=0.82; 일치키워드=아이템,워크셀,태스크,파일; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.57; 의미유사도=0.82; 일치키워드=아이템,워크셀,태스크,파일; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -25503,7 +25503,7 @@
       </c>
       <c r="U241" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.58; 일치키워드=데이터,아이템,워크셀,태스크,파일; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.58; 일치키워드=데이터,아이템,워크셀,태스크,파일; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -25615,7 +25615,7 @@
       </c>
       <c r="U242" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.57; 의미유사도=0.60; 일치키워드=아이템,워크셀,태스크,파일; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.57; 의미유사도=0.60; 일치키워드=아이템,워크셀,태스크,파일; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -25722,7 +25722,7 @@
       </c>
       <c r="U243" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.57; 의미유사도=0.82; 일치키워드=아이템,워크셀,태스크,파일; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.57; 의미유사도=0.82; 일치키워드=아이템,워크셀,태스크,파일; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -25829,7 +25829,7 @@
       </c>
       <c r="U244" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.86; 의미유사도=0.70; 일치키워드=데이터,베이스,아이템,워크셀,태스크,파일; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.86; 의미유사도=0.70; 일치키워드=데이터,베이스,아이템,워크셀,태스크,파일; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -25932,7 +25932,7 @@
       </c>
       <c r="U245" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.28; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.28; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -26035,7 +26035,7 @@
       </c>
       <c r="U246" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.29; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.29; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -26138,7 +26138,7 @@
       </c>
       <c r="U247" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.30; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.30; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -26241,7 +26241,7 @@
       </c>
       <c r="U248" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.28; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.28; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -26344,7 +26344,7 @@
       </c>
       <c r="U249" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.30; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.30; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -26447,7 +26447,7 @@
       </c>
       <c r="U250" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.31; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.31; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -26550,7 +26550,7 @@
       </c>
       <c r="U251" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.62; 일치키워드=grommet,그로밋; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.62; 일치키워드=grommet,그로밋; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -26653,7 +26653,7 @@
       </c>
       <c r="U252" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.29; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.29; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -26756,7 +26756,7 @@
       </c>
       <c r="U253" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.90; 일치키워드=grommet,그로밋; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.90; 일치키워드=grommet,그로밋; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -26873,7 +26873,7 @@
       </c>
       <c r="U254" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.65; 일치키워드=플랜지; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.65; 일치키워드=플랜지; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -26976,7 +26976,7 @@
       </c>
       <c r="U255" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.79; 일치키워드=좌표계의,플랜지; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.79; 일치키워드=좌표계의,플랜지; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -27079,7 +27079,7 @@
       </c>
       <c r="U256" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.79; 일치키워드=좌표계의,플랜지; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.79; 일치키워드=좌표계의,플랜지; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -27186,7 +27186,7 @@
       </c>
       <c r="U257" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.69; 일치키워드=좌표계의,플랜지; 텍스트순위=1; 이미지순위=4</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.69; 일치키워드=좌표계의,플랜지; 텍스트순위=1; 이미지순위=4</t>
         </is>
       </c>
     </row>
@@ -27293,7 +27293,7 @@
       </c>
       <c r="U258" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.79; 일치키워드=좌표계의,플랜지; 텍스트순위=1; 이미지순위=4</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.79; 일치키워드=좌표계의,플랜지; 텍스트순위=1; 이미지순위=4</t>
         </is>
       </c>
     </row>
@@ -27400,7 +27400,7 @@
       </c>
       <c r="U259" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.79; 일치키워드=좌표계의,플랜지; 텍스트순위=1; 이미지순위=4</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.79; 일치키워드=좌표계의,플랜지; 텍스트순위=1; 이미지순위=4</t>
         </is>
       </c>
     </row>
@@ -27507,7 +27507,7 @@
       </c>
       <c r="U260" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.71; 일치키워드=좌표계의,플랜지; 텍스트순위=1; 이미지순위=4</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.71; 일치키워드=좌표계의,플랜지; 텍스트순위=1; 이미지순위=4</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="U261" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.79; 일치키워드=좌표계의,플랜지; 텍스트순위=1; 이미지순위=4</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.79; 일치키워드=좌표계의,플랜지; 텍스트순위=1; 이미지순위=4</t>
         </is>
       </c>
     </row>
@@ -27721,7 +27721,7 @@
       </c>
       <c r="U262" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.79; 일치키워드=좌표계의,플랜지; 텍스트순위=1; 이미지순위=4</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.79; 일치키워드=좌표계의,플랜지; 텍스트순위=1; 이미지순위=4</t>
         </is>
       </c>
     </row>
@@ -27831,7 +27831,7 @@
       </c>
       <c r="U263" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.17; 의미유사도=0.72; 일치키워드=극성이; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.17; 의미유사도=0.72; 일치키워드=극성이; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -27934,7 +27934,7 @@
       </c>
       <c r="U264" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.17; 의미유사도=0.63; 일치키워드=극성이; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.17; 의미유사도=0.63; 일치키워드=극성이; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -28038,7 +28038,7 @@
       </c>
       <c r="U265" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.61; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.61; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -28148,7 +28148,7 @@
       </c>
       <c r="U266" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.17; 의미유사도=0.72; 일치키워드=극성이; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.17; 의미유사도=0.72; 일치키워드=극성이; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -28251,7 +28251,7 @@
       </c>
       <c r="U267" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.17; 의미유사도=0.63; 일치키워드=극성이; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.17; 의미유사도=0.63; 일치키워드=극성이; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -28355,7 +28355,7 @@
       </c>
       <c r="U268" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.61; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.61; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -28469,7 +28469,7 @@
       </c>
       <c r="U269" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.17; 의미유사도=0.71; 일치키워드=극성이; 텍스트순위=1; 이미지순위=8</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.17; 의미유사도=0.71; 일치키워드=극성이; 텍스트순위=1; 이미지순위=8</t>
         </is>
       </c>
     </row>
@@ -28576,7 +28576,7 @@
       </c>
       <c r="U270" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.17; 의미유사도=0.63; 일치키워드=극성이; 텍스트순위=1; 이미지순위=8</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.17; 의미유사도=0.63; 일치키워드=극성이; 텍스트순위=1; 이미지순위=8</t>
         </is>
       </c>
     </row>
@@ -28685,7 +28685,7 @@
       </c>
       <c r="U271" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.59; 일치키워드=; 텍스트순위=1; 이미지순위=8</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.59; 일치키워드=; 텍스트순위=1; 이미지순위=8</t>
         </is>
       </c>
     </row>
@@ -28788,7 +28788,7 @@
       </c>
       <c r="U272" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.62; 일치키워드=내보내기,태스크; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.62; 일치키워드=내보내기,태스크; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -28891,7 +28891,7 @@
       </c>
       <c r="U273" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.80; 일치키워드=내보내기,태스크; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.80; 일치키워드=내보내기,태스크; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -28994,7 +28994,7 @@
       </c>
       <c r="U274" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.80; 일치키워드=내보내기,태스크; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.80; 일치키워드=내보내기,태스크; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -29097,7 +29097,7 @@
       </c>
       <c r="U275" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.62; 일치키워드=내보내기,태스크; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.62; 일치키워드=내보내기,태스크; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -29200,7 +29200,7 @@
       </c>
       <c r="U276" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.80; 일치키워드=내보내기,태스크; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.80; 일치키워드=내보내기,태스크; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -29303,7 +29303,7 @@
       </c>
       <c r="U277" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.80; 일치키워드=내보내기,태스크; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.80; 일치키워드=내보내기,태스크; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -29410,7 +29410,7 @@
       </c>
       <c r="U278" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.62; 일치키워드=내보내기,태스크; 텍스트순위=1; 이미지순위=3</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.62; 일치키워드=내보내기,태스크; 텍스트순위=1; 이미지순위=3</t>
         </is>
       </c>
     </row>
@@ -29517,7 +29517,7 @@
       </c>
       <c r="U279" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.41; 일치키워드=; 텍스트순위=1; 이미지순위=3</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.41; 일치키워드=; 텍스트순위=1; 이미지순위=3</t>
         </is>
       </c>
     </row>
@@ -29624,7 +29624,7 @@
       </c>
       <c r="U280" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.62; 일치키워드=내보내기,태스크; 텍스트순위=1; 이미지순위=3</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.62; 일치키워드=내보내기,태스크; 텍스트순위=1; 이미지순위=3</t>
         </is>
       </c>
     </row>
@@ -29729,7 +29729,7 @@
       </c>
       <c r="U281" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.47; 일치키워드=; 텍스트순위=7; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.47; 일치키워드=; 텍스트순위=7; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -29832,7 +29832,7 @@
       </c>
       <c r="U282" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.41; 일치키워드=; 텍스트순위=7; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.41; 일치키워드=; 텍스트순위=7; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -29935,7 +29935,7 @@
       </c>
       <c r="U283" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.42; 일치키워드=; 텍스트순위=7; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.42; 일치키워드=; 텍스트순위=7; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -30044,7 +30044,7 @@
       </c>
       <c r="U284" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.00; 일치키워드=; 텍스트순위=7; 이미지순위=6</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.00; 일치키워드=; 텍스트순위=7; 이미지순위=6</t>
         </is>
       </c>
     </row>
@@ -30151,7 +30151,7 @@
       </c>
       <c r="U285" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.40; 일치키워드=; 텍스트순위=7; 이미지순위=6</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.40; 일치키워드=; 텍스트순위=7; 이미지순위=6</t>
         </is>
       </c>
     </row>
@@ -30258,7 +30258,7 @@
       </c>
       <c r="U286" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.42; 일치키워드=; 텍스트순위=7; 이미지순위=6</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.42; 일치키워드=; 텍스트순위=7; 이미지순위=6</t>
         </is>
       </c>
     </row>
@@ -30366,7 +30366,7 @@
       </c>
       <c r="U287" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.45; 일치키워드=; 텍스트순위=7; 이미지순위=6</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.45; 일치키워드=; 텍스트순위=7; 이미지순위=6</t>
         </is>
       </c>
     </row>
@@ -30473,7 +30473,7 @@
       </c>
       <c r="U288" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.37; 일치키워드=; 텍스트순위=7; 이미지순위=6</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.37; 일치키워드=; 텍스트순위=7; 이미지순위=6</t>
         </is>
       </c>
     </row>
@@ -30580,7 +30580,7 @@
       </c>
       <c r="U289" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.41; 일치키워드=; 텍스트순위=7; 이미지순위=6</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.41; 일치키워드=; 텍스트순위=7; 이미지순위=6</t>
         </is>
       </c>
     </row>
@@ -30683,7 +30683,7 @@
       </c>
       <c r="U290" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.62; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.62; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -30786,7 +30786,7 @@
       </c>
       <c r="U291" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.58; 일치키워드=admin; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.58; 일치키워드=admin; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -30889,7 +30889,7 @@
       </c>
       <c r="U292" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.54; 일치키워드=admin; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.54; 일치키워드=admin; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -30996,7 +30996,7 @@
       </c>
       <c r="U293" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.62; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.62; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -31103,7 +31103,7 @@
       </c>
       <c r="U294" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.58; 일치키워드=admin; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.58; 일치키워드=admin; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -31210,7 +31210,7 @@
       </c>
       <c r="U295" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.59; 일치키워드=admin; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.59; 일치키워드=admin; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -31317,7 +31317,7 @@
       </c>
       <c r="U296" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.62; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.62; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -31424,7 +31424,7 @@
       </c>
       <c r="U297" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.58; 일치키워드=admin; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.58; 일치키워드=admin; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -31531,7 +31531,7 @@
       </c>
       <c r="U298" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.59; 일치키워드=admin; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.59; 일치키워드=admin; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -31634,7 +31634,7 @@
       </c>
       <c r="U299" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.68; 일치키워드=모드,패키징; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.68; 일치키워드=모드,패키징; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -31737,7 +31737,7 @@
       </c>
       <c r="U300" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=1.00; 일치키워드=모드,패키징; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=1.00; 일치키워드=모드,패키징; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -31840,7 +31840,7 @@
       </c>
       <c r="U301" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.90; 일치키워드=패키징; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.90; 일치키워드=패키징; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -31947,7 +31947,7 @@
       </c>
       <c r="U302" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.68; 일치키워드=모드,패키징; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.68; 일치키워드=모드,패키징; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -32054,7 +32054,7 @@
       </c>
       <c r="U303" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=1.00; 일치키워드=모드,패키징; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=1.00; 일치키워드=모드,패키징; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -32161,7 +32161,7 @@
       </c>
       <c r="U304" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.90; 일치키워드=패키징; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.90; 일치키워드=패키징; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -32268,7 +32268,7 @@
       </c>
       <c r="U305" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.74; 일치키워드=패키징; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.74; 일치키워드=패키징; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -32375,7 +32375,7 @@
       </c>
       <c r="U306" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=1.00; 일치키워드=모드,패키징; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=1.00; 일치키워드=모드,패키징; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -32482,7 +32482,7 @@
       </c>
       <c r="U307" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.90; 일치키워드=패키징; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.90; 일치키워드=패키징; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -32585,7 +32585,7 @@
       </c>
       <c r="U308" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.48; 일치키워드=gio,gnd; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.48; 일치키워드=gio,gnd; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -32688,7 +32688,7 @@
       </c>
       <c r="U309" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.32; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.32; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -32792,7 +32792,7 @@
       </c>
       <c r="U310" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.48; 일치키워드=gnd,vcc,vio; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.48; 일치키워드=gnd,vcc,vio; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -32899,7 +32899,7 @@
       </c>
       <c r="U311" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.49; 일치키워드=gio,gnd; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.49; 일치키워드=gio,gnd; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -33006,7 +33006,7 @@
       </c>
       <c r="U312" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.32; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.32; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -33113,7 +33113,7 @@
       </c>
       <c r="U313" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.43; 일치키워드=gio; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.43; 일치키워드=gio; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -33220,7 +33220,7 @@
       </c>
       <c r="U314" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.56; 일치키워드=gio,gnd,vio; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.56; 일치키워드=gio,gnd,vio; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -33327,7 +33327,7 @@
       </c>
       <c r="U315" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.34; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.34; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -33436,7 +33436,7 @@
       </c>
       <c r="U316" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.38; 일치키워드=gio,vio; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.38; 일치키워드=gio,vio; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -33543,7 +33543,7 @@
       </c>
       <c r="U317" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.57; 일치키워드=기준점,위의; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.57; 일치키워드=기준점,위의; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -33649,7 +33649,7 @@
       </c>
       <c r="U318" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.64; 일치키워드=x축,기준점,위의; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.64; 일치키워드=x축,기준점,위의; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -33756,7 +33756,7 @@
       </c>
       <c r="U319" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.57; 일치키워드=기준점,위의; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.57; 일치키워드=기준점,위의; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -33867,7 +33867,7 @@
       </c>
       <c r="U320" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.55; 일치키워드=기준점,위의; 텍스트순위=1; 이미지순위=10</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.55; 일치키워드=기준점,위의; 텍스트순위=1; 이미지순위=10</t>
         </is>
       </c>
     </row>
@@ -33977,7 +33977,7 @@
       </c>
       <c r="U321" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.64; 일치키워드=기준점,위의; 텍스트순위=1; 이미지순위=10</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.64; 일치키워드=기준점,위의; 텍스트순위=1; 이미지순위=10</t>
         </is>
       </c>
     </row>
@@ -34088,7 +34088,7 @@
       </c>
       <c r="U322" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.59; 일치키워드=기준점,위의; 텍스트순위=1; 이미지순위=10</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.59; 일치키워드=기준점,위의; 텍스트순위=1; 이미지순위=10</t>
         </is>
       </c>
     </row>
@@ -34199,7 +34199,7 @@
       </c>
       <c r="U323" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.61; 일치키워드=x축,기준점,위의; 텍스트순위=1; 이미지순위=9</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.61; 일치키워드=x축,기준점,위의; 텍스트순위=1; 이미지순위=9</t>
         </is>
       </c>
     </row>
@@ -34309,7 +34309,7 @@
       </c>
       <c r="U324" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.64; 일치키워드=x축,기준점,위의; 텍스트순위=1; 이미지순위=9</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.64; 일치키워드=x축,기준점,위의; 텍스트순위=1; 이미지순위=9</t>
         </is>
       </c>
     </row>
@@ -34420,7 +34420,7 @@
       </c>
       <c r="U325" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.57; 일치키워드=기준점,위의; 텍스트순위=1; 이미지순위=9</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.57; 일치키워드=기준점,위의; 텍스트순위=1; 이미지순위=9</t>
         </is>
       </c>
     </row>
@@ -34523,7 +34523,7 @@
       </c>
       <c r="U326" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.73; 일치키워드=external,force,reset,set; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.73; 일치키워드=external,force,reset,set; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -34626,7 +34626,7 @@
       </c>
       <c r="U327" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=1.00; 일치키워드=external,force,reset,set; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=1.00; 일치키워드=external,force,reset,set; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -34729,7 +34729,7 @@
       </c>
       <c r="U328" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=1.00; 일치키워드=external,force,reset,set; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=1.00; 일치키워드=external,force,reset,set; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -34832,7 +34832,7 @@
       </c>
       <c r="U329" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.73; 일치키워드=external,force,reset,set; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.73; 일치키워드=external,force,reset,set; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -34935,7 +34935,7 @@
       </c>
       <c r="U330" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=1.00; 일치키워드=external,force,reset,set; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=1.00; 일치키워드=external,force,reset,set; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -35038,7 +35038,7 @@
       </c>
       <c r="U331" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=1.00; 일치키워드=external,force,reset,set; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=1.00; 일치키워드=external,force,reset,set; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -35145,7 +35145,7 @@
       </c>
       <c r="U332" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.71; 일치키워드=external,force,reset,set; 텍스트순위=1; 이미지순위=6</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.71; 일치키워드=external,force,reset,set; 텍스트순위=1; 이미지순위=6</t>
         </is>
       </c>
     </row>
@@ -35252,7 +35252,7 @@
       </c>
       <c r="U333" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=1.00; 일치키워드=external,force,reset,set; 텍스트순위=1; 이미지순위=6</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=1.00; 일치키워드=external,force,reset,set; 텍스트순위=1; 이미지순위=6</t>
         </is>
       </c>
     </row>
@@ -35359,7 +35359,7 @@
       </c>
       <c r="U334" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=1.00; 일치키워드=external,force,reset,set; 텍스트순위=1; 이미지순위=6</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=1.00; 일치키워드=external,force,reset,set; 텍스트순위=1; 이미지순위=6</t>
         </is>
       </c>
     </row>
@@ -35462,7 +35462,7 @@
       </c>
       <c r="U335" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.63; 일치키워드=slot; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.63; 일치키워드=slot; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -35565,7 +35565,7 @@
       </c>
       <c r="U336" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.92; 일치키워드=slot; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.92; 일치키워드=slot; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -35668,7 +35668,7 @@
       </c>
       <c r="U337" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.70; 일치키워드=slot; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.70; 일치키워드=slot; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -35775,7 +35775,7 @@
       </c>
       <c r="U338" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.63; 일치키워드=slot; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.63; 일치키워드=slot; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -35882,7 +35882,7 @@
       </c>
       <c r="U339" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.92; 일치키워드=slot; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.92; 일치키워드=slot; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -35989,7 +35989,7 @@
       </c>
       <c r="U340" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.73; 일치키워드=slot; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.73; 일치키워드=slot; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -36096,7 +36096,7 @@
       </c>
       <c r="U341" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.63; 일치키워드=slot; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.63; 일치키워드=slot; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -36203,7 +36203,7 @@
       </c>
       <c r="U342" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.92; 일치키워드=slot; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.92; 일치키워드=slot; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -36310,7 +36310,7 @@
       </c>
       <c r="U343" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.73; 일치키워드=slot; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.73; 일치키워드=slot; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -36413,7 +36413,7 @@
       </c>
       <c r="U344" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.40; 의미유사도=0.81; 일치키워드=상자에,컨트롤러는; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.40; 의미유사도=0.81; 일치키워드=상자에,컨트롤러는; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -36516,7 +36516,7 @@
       </c>
       <c r="U345" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.40; 의미유사도=0.81; 일치키워드=2개의,상자에; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.40; 의미유사도=0.81; 일치키워드=2개의,상자에; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -36619,7 +36619,7 @@
       </c>
       <c r="U346" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.40; 의미유사도=0.84; 일치키워드=2개의,상자에; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.40; 의미유사도=0.84; 일치키워드=2개의,상자에; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -36726,7 +36726,7 @@
       </c>
       <c r="U347" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.40; 의미유사도=0.82; 일치키워드=상자에,컨트롤러는; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.40; 의미유사도=0.82; 일치키워드=상자에,컨트롤러는; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -36833,7 +36833,7 @@
       </c>
       <c r="U348" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.40; 의미유사도=0.81; 일치키워드=2개의,상자에; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.40; 의미유사도=0.81; 일치키워드=2개의,상자에; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -36940,7 +36940,7 @@
       </c>
       <c r="U349" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.40; 의미유사도=0.84; 일치키워드=2개의,상자에; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.40; 의미유사도=0.84; 일치키워드=2개의,상자에; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -37047,7 +37047,7 @@
       </c>
       <c r="U350" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.40; 의미유사도=0.82; 일치키워드=상자에,컨트롤러는; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.40; 의미유사도=0.82; 일치키워드=상자에,컨트롤러는; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -37154,7 +37154,7 @@
       </c>
       <c r="U351" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.40; 의미유사도=0.81; 일치키워드=2개의,상자에; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.40; 의미유사도=0.81; 일치키워드=2개의,상자에; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -37261,7 +37261,7 @@
       </c>
       <c r="U352" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.84; 일치키워드=상자에; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.84; 일치키워드=상자에; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -37367,7 +37367,7 @@
       </c>
       <c r="U353" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.67; 일치키워드=딸깍,때까지,소리가,연결부에,연결해야,해당; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.67; 일치키워드=딸깍,때까지,소리가,연결부에,연결해야,해당; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -37470,7 +37470,7 @@
       </c>
       <c r="U354" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.72; 일치키워드=딸깍,때까지,소리가,연결부에; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.72; 일치키워드=딸깍,때까지,소리가,연결부에; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -37578,7 +37578,7 @@
       </c>
       <c r="U355" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.52; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.52; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -37688,7 +37688,7 @@
       </c>
       <c r="U356" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.66; 일치키워드=딸깍,때까지,소리가,연결부에,해당; 텍스트순위=1; 이미지순위=3</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.66; 일치키워드=딸깍,때까지,소리가,연결부에,해당; 텍스트순위=1; 이미지순위=3</t>
         </is>
       </c>
     </row>
@@ -37795,7 +37795,7 @@
       </c>
       <c r="U357" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.72; 일치키워드=딸깍,때까지,소리가,연결부에; 텍스트순위=1; 이미지순위=3</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.72; 일치키워드=딸깍,때까지,소리가,연결부에; 텍스트순위=1; 이미지순위=3</t>
         </is>
       </c>
     </row>
@@ -37907,7 +37907,7 @@
       </c>
       <c r="U358" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.61; 일치키워드=딸깍,소리가; 텍스트순위=1; 이미지순위=3</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.61; 일치키워드=딸깍,소리가; 텍스트순위=1; 이미지순위=3</t>
         </is>
       </c>
     </row>
@@ -38017,7 +38017,7 @@
       </c>
       <c r="U359" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.68; 일치키워드=딸깍,때까지,소리가,연결부에,연결해야,해당; 텍스트순위=1; 이미지순위=3</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.68; 일치키워드=딸깍,때까지,소리가,연결부에,연결해야,해당; 텍스트순위=1; 이미지순위=3</t>
         </is>
       </c>
     </row>
@@ -38124,7 +38124,7 @@
       </c>
       <c r="U360" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.70; 일치키워드=딸깍,때까지,소리가; 텍스트순위=1; 이미지순위=3</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.70; 일치키워드=딸깍,때까지,소리가; 텍스트순위=1; 이미지순위=3</t>
         </is>
       </c>
     </row>
@@ -38234,7 +38234,7 @@
       </c>
       <c r="U361" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.62; 일치키워드=딸깍,때까지,소리가,연결부에,해당; 텍스트순위=1; 이미지순위=3</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.62; 일치키워드=딸깍,때까지,소리가,연결부에,해당; 텍스트순위=1; 이미지순위=3</t>
         </is>
       </c>
     </row>
@@ -38338,7 +38338,7 @@
       </c>
       <c r="U362" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.71; 일치키워드=로봇이,올바르게,확인해야; 텍스트순위=2; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.71; 일치키워드=로봇이,올바르게,확인해야; 텍스트순위=2; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -38441,7 +38441,7 @@
       </c>
       <c r="U363" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.85; 일치키워드=로봇이,올바르게,접지되었는지; 텍스트순위=2; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.85; 일치키워드=로봇이,올바르게,접지되었는지; 텍스트순위=2; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -38544,7 +38544,7 @@
       </c>
       <c r="U364" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.44; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.44; 일치키워드=; 텍스트순위=2; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -38651,7 +38651,7 @@
       </c>
       <c r="U365" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.63; 일치키워드=확인해야; 텍스트순위=2; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.63; 일치키워드=확인해야; 텍스트순위=2; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -38758,7 +38758,7 @@
       </c>
       <c r="U366" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.85; 일치키워드=로봇이,올바르게,접지되었는지; 텍스트순위=2; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.85; 일치키워드=로봇이,올바르게,접지되었는지; 텍스트순위=2; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -38865,7 +38865,7 @@
       </c>
       <c r="U367" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.44; 일치키워드=; 텍스트순위=2; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.44; 일치키워드=; 텍스트순위=2; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -38976,7 +38976,7 @@
       </c>
       <c r="U368" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.68; 일치키워드=로봇이,올바르게,접지되었는지,확인해야; 텍스트순위=2; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.68; 일치키워드=로봇이,올바르게,접지되었는지,확인해야; 텍스트순위=2; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -39083,7 +39083,7 @@
       </c>
       <c r="U369" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.85; 일치키워드=로봇이,올바르게,접지되었는지; 텍스트순위=2; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.85; 일치키워드=로봇이,올바르게,접지되었는지; 텍스트순위=2; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -39190,7 +39190,7 @@
       </c>
       <c r="U370" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.44; 일치키워드=; 텍스트순위=2; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.44; 일치키워드=; 텍스트순위=2; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -39293,7 +39293,7 @@
       </c>
       <c r="U371" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.57; 의미유사도=0.70; 일치키워드=50,공간을,양쪽,여유; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.57; 의미유사도=0.70; 일치키워드=50,공간을,양쪽,여유; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -39396,7 +39396,7 @@
       </c>
       <c r="U372" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.72; 일치키워드=50; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.72; 일치키워드=50; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -39499,7 +39499,7 @@
       </c>
       <c r="U373" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.72; 일치키워드=50; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.72; 일치키워드=50; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -39606,7 +39606,7 @@
       </c>
       <c r="U374" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.57; 의미유사도=0.70; 일치키워드=50,공간을,양쪽,여유; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.57; 의미유사도=0.70; 일치키워드=50,공간을,양쪽,여유; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -39713,7 +39713,7 @@
       </c>
       <c r="U375" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.72; 일치키워드=50; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.72; 일치키워드=50; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -39820,7 +39820,7 @@
       </c>
       <c r="U376" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.43; 의미유사도=0.89; 일치키워드=50,공간을,여유; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.43; 의미유사도=0.89; 일치키워드=50,공간을,여유; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -39927,7 +39927,7 @@
       </c>
       <c r="U377" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.57; 의미유사도=0.70; 일치키워드=50,공간을,양쪽,여유; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.57; 의미유사도=0.70; 일치키워드=50,공간을,양쪽,여유; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -40034,7 +40034,7 @@
       </c>
       <c r="U378" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.74; 일치키워드=50; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.74; 일치키워드=50; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -40141,7 +40141,7 @@
       </c>
       <c r="U379" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.43; 의미유사도=0.89; 일치키워드=50,공간을,여유; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.43; 의미유사도=0.89; 일치키워드=50,공간을,여유; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -40244,7 +40244,7 @@
       </c>
       <c r="U380" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.64; 일치키워드=방향으로,버튼을,비상,시계,정지; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.64; 일치키워드=방향으로,버튼을,비상,시계,정지; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -40347,7 +40347,7 @@
       </c>
       <c r="U381" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.89; 일치키워드=방향으로,버튼을,비상,시계,정지; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.89; 일치키워드=방향으로,버튼을,비상,시계,정지; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -40450,7 +40450,7 @@
       </c>
       <c r="U382" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.89; 일치키워드=방향으로,버튼을,비상,시계,정지; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.89; 일치키워드=방향으로,버튼을,비상,시계,정지; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -40557,7 +40557,7 @@
       </c>
       <c r="U383" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.64; 일치키워드=방향으로,버튼을,비상,시계,정지; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.64; 일치키워드=방향으로,버튼을,비상,시계,정지; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -40664,7 +40664,7 @@
       </c>
       <c r="U384" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.89; 일치키워드=방향으로,버튼을,비상,시계,정지; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.89; 일치키워드=방향으로,버튼을,비상,시계,정지; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -40771,7 +40771,7 @@
       </c>
       <c r="U385" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.89; 일치키워드=방향으로,버튼을,비상,시계,정지; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.89; 일치키워드=방향으로,버튼을,비상,시계,정지; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -40878,7 +40878,7 @@
       </c>
       <c r="U386" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.64; 일치키워드=방향으로,버튼을,비상,시계,정지; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.64; 일치키워드=방향으로,버튼을,비상,시계,정지; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -40985,7 +40985,7 @@
       </c>
       <c r="U387" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.89; 일치키워드=방향으로,버튼을,비상,시계,정지; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.89; 일치키워드=방향으로,버튼을,비상,시계,정지; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -41092,7 +41092,7 @@
       </c>
       <c r="U388" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.89; 일치키워드=방향으로,버튼을,비상,시계,정지; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.89; 일치키워드=방향으로,버튼을,비상,시계,정지; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -41195,7 +41195,7 @@
       </c>
       <c r="U389" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.85; 일치키워드=전원,종료,팝업에서; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.85; 일치키워드=전원,종료,팝업에서; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -41298,7 +41298,7 @@
       </c>
       <c r="U390" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.73; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.73; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -41401,7 +41401,7 @@
       </c>
       <c r="U391" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.71; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.71; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -41508,7 +41508,7 @@
       </c>
       <c r="U392" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.85; 일치키워드=전원,종료,팝업에서; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.85; 일치키워드=전원,종료,팝업에서; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -41615,7 +41615,7 @@
       </c>
       <c r="U393" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.73; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.73; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -41722,7 +41722,7 @@
       </c>
       <c r="U394" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.71; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.71; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -41829,7 +41829,7 @@
       </c>
       <c r="U395" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.85; 일치키워드=전원,종료,팝업에서; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.85; 일치키워드=전원,종료,팝업에서; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -41936,7 +41936,7 @@
       </c>
       <c r="U396" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.73; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.73; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -42043,7 +42043,7 @@
       </c>
       <c r="U397" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.71; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.71; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -42146,7 +42146,7 @@
       </c>
       <c r="U398" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.12; 의미유사도=0.58; 일치키워드=표시된; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.12; 의미유사도=0.58; 일치키워드=표시된; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -42249,7 +42249,7 @@
       </c>
       <c r="U399" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.12; 의미유사도=0.74; 일치키워드=표시된; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.12; 의미유사도=0.74; 일치키워드=표시된; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -42352,7 +42352,7 @@
       </c>
       <c r="U400" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.71; 일치키워드=들어,표시된; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.71; 일치키워드=들어,표시된; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -42459,7 +42459,7 @@
       </c>
       <c r="U401" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.12; 의미유사도=0.59; 일치키워드=표시된; 텍스트순위=1; 이미지순위=5</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.12; 의미유사도=0.59; 일치키워드=표시된; 텍스트순위=1; 이미지순위=5</t>
         </is>
       </c>
     </row>
@@ -42566,7 +42566,7 @@
       </c>
       <c r="U402" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.12; 의미유사도=0.74; 일치키워드=표시된; 텍스트순위=1; 이미지순위=5</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.12; 의미유사도=0.74; 일치키워드=표시된; 텍스트순위=1; 이미지순위=5</t>
         </is>
       </c>
     </row>
@@ -42675,7 +42675,7 @@
       </c>
       <c r="U403" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.12; 의미유사도=0.44; 일치키워드=들어; 텍스트순위=1; 이미지순위=5</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.12; 의미유사도=0.44; 일치키워드=들어; 텍스트순위=1; 이미지순위=5</t>
         </is>
       </c>
     </row>
@@ -42782,7 +42782,7 @@
       </c>
       <c r="U404" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.12; 의미유사도=0.58; 일치키워드=표시된; 텍스트순위=1; 이미지순위=5</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.12; 의미유사도=0.58; 일치키워드=표시된; 텍스트순위=1; 이미지순위=5</t>
         </is>
       </c>
     </row>
@@ -42889,7 +42889,7 @@
       </c>
       <c r="U405" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.12; 의미유사도=0.74; 일치키워드=표시된; 텍스트순위=1; 이미지순위=5</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.12; 의미유사도=0.74; 일치키워드=표시된; 텍스트순위=1; 이미지순위=5</t>
         </is>
       </c>
     </row>
@@ -42996,7 +42996,7 @@
       </c>
       <c r="U406" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.12; 의미유사도=0.60; 일치키워드=인양; 텍스트순위=1; 이미지순위=5</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.12; 의미유사도=0.60; 일치키워드=인양; 텍스트순위=1; 이미지순위=5</t>
         </is>
       </c>
     </row>
@@ -43099,7 +43099,7 @@
       </c>
       <c r="U407" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.74; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.74; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -43202,7 +43202,7 @@
       </c>
       <c r="U408" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.75; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.75; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -43305,7 +43305,7 @@
       </c>
       <c r="U409" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.80; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.80; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -43412,7 +43412,7 @@
       </c>
       <c r="U410" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.74; 일치키워드=; 텍스트순위=1; 이미지순위=3</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.74; 일치키워드=; 텍스트순위=1; 이미지순위=3</t>
         </is>
       </c>
     </row>
@@ -43519,7 +43519,7 @@
       </c>
       <c r="U411" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.67; 일치키워드=; 텍스트순위=1; 이미지순위=3</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.67; 일치키워드=; 텍스트순위=1; 이미지순위=3</t>
         </is>
       </c>
     </row>
@@ -43626,7 +43626,7 @@
       </c>
       <c r="U412" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.80; 일치키워드=; 텍스트순위=1; 이미지순위=3</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.80; 일치키워드=; 텍스트순위=1; 이미지순위=3</t>
         </is>
       </c>
     </row>
@@ -43733,7 +43733,7 @@
       </c>
       <c r="U413" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.74; 일치키워드=; 텍스트순위=2; 이미지순위=3</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.74; 일치키워드=; 텍스트순위=2; 이미지순위=3</t>
         </is>
       </c>
     </row>
@@ -43840,7 +43840,7 @@
       </c>
       <c r="U414" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.75; 일치키워드=; 텍스트순위=2; 이미지순위=3</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.75; 일치키워드=; 텍스트순위=2; 이미지순위=3</t>
         </is>
       </c>
     </row>
@@ -43947,7 +43947,7 @@
       </c>
       <c r="U415" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.80; 일치키워드=; 텍스트순위=2; 이미지순위=3</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.80; 일치키워드=; 텍스트순위=2; 이미지순위=3</t>
         </is>
       </c>
     </row>
@@ -44050,7 +44050,7 @@
       </c>
       <c r="U416" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.69; 일치키워드=고리를,고정용,연결; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.69; 일치키워드=고리를,고정용,연결; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -44153,7 +44153,7 @@
       </c>
       <c r="U417" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.73; 일치키워드=고리를,고정용; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.73; 일치키워드=고리를,고정용; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -44256,7 +44256,7 @@
       </c>
       <c r="U418" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.69; 일치키워드=고리를,고정용,연결; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.69; 일치키워드=고리를,고정용,연결; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -44363,7 +44363,7 @@
       </c>
       <c r="U419" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.71; 일치키워드=고리를,고정용,연결; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.71; 일치키워드=고리를,고정용,연결; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -44470,7 +44470,7 @@
       </c>
       <c r="U420" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.73; 일치키워드=고리를,고정용; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.73; 일치키워드=고리를,고정용; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -44577,7 +44577,7 @@
       </c>
       <c r="U421" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.73; 일치키워드=고리를,고정용; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.73; 일치키워드=고리를,고정용; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -44684,7 +44684,7 @@
       </c>
       <c r="U422" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.24; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.24; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -44791,7 +44791,7 @@
       </c>
       <c r="U423" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.73; 일치키워드=고리를,고정용; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.73; 일치키워드=고리를,고정용; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -44898,7 +44898,7 @@
       </c>
       <c r="U424" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.73; 일치키워드=고리를,고정용; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.73; 일치키워드=고리를,고정용; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -45001,7 +45001,7 @@
       </c>
       <c r="U425" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.11; 의미유사도=0.68; 일치키워드=볼트; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.11; 의미유사도=0.68; 일치키워드=볼트; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -45104,7 +45104,7 @@
       </c>
       <c r="U426" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.72; 일치키워드=m6,nm,볼트; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.72; 일치키워드=m6,nm,볼트; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -45207,7 +45207,7 @@
       </c>
       <c r="U427" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.68; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.68; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -45314,7 +45314,7 @@
       </c>
       <c r="U428" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.11; 의미유사도=0.68; 일치키워드=볼트; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.11; 의미유사도=0.68; 일치키워드=볼트; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -45421,7 +45421,7 @@
       </c>
       <c r="U429" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.56; 의미유사도=0.72; 일치키워드=4개를,m6,nm,볼트,사용하며; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.56; 의미유사도=0.72; 일치키워드=4개를,m6,nm,볼트,사용하며; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -45528,7 +45528,7 @@
       </c>
       <c r="U430" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.11; 의미유사도=0.67; 일치키워드=볼트; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.11; 의미유사도=0.67; 일치키워드=볼트; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -45635,7 +45635,7 @@
       </c>
       <c r="U431" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.11; 의미유사도=0.68; 일치키워드=볼트; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.11; 의미유사도=0.68; 일치키워드=볼트; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -45742,7 +45742,7 @@
       </c>
       <c r="U432" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.78; 의미유사도=0.82; 일치키워드=4개를,m6,것을,볼트,사용하며,조이는,토크로; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.78; 의미유사도=0.82; 일치키워드=4개를,m6,것을,볼트,사용하며,조이는,토크로; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -45849,7 +45849,7 @@
       </c>
       <c r="U433" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.84; 일치키워드=m6,nm,것을,볼트,조이는,토크로; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.84; 일치키워드=m6,nm,것을,볼트,조이는,토크로; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -45952,7 +45952,7 @@
       </c>
       <c r="U434" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.72; 일치키워드=스위치를,전원; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.72; 일치키워드=스위치를,전원; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -46055,7 +46055,7 @@
       </c>
       <c r="U435" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.83; 일치키워드=스위치를,전원; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.83; 일치키워드=스위치를,전원; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -46158,7 +46158,7 @@
       </c>
       <c r="U436" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.78; 일치키워드=전원; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.78; 일치키워드=전원; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -46265,7 +46265,7 @@
       </c>
       <c r="U437" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.73; 일치키워드=스위치를,전원; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.73; 일치키워드=스위치를,전원; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -46372,7 +46372,7 @@
       </c>
       <c r="U438" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.83; 일치키워드=스위치를,전원; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.83; 일치키워드=스위치를,전원; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -46479,7 +46479,7 @@
       </c>
       <c r="U439" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.78; 일치키워드=전원; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.78; 일치키워드=전원; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -46586,7 +46586,7 @@
       </c>
       <c r="U440" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.72; 일치키워드=스위치를,전원; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.72; 일치키워드=스위치를,전원; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -46693,7 +46693,7 @@
       </c>
       <c r="U441" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.83; 일치키워드=스위치를,전원; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.83; 일치키워드=스위치를,전원; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -46800,7 +46800,7 @@
       </c>
       <c r="U442" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.75; 일치키워드=전원; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.75; 일치키워드=전원; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -46903,7 +46903,7 @@
       </c>
       <c r="U443" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.78; 일치키워드=24v가,open; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.78; 일치키워드=24v가,open; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -47006,7 +47006,7 @@
       </c>
       <c r="U444" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.79; 일치키워드=24v가,open,되고; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.79; 일치키워드=24v가,open,되고; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -47109,7 +47109,7 @@
       </c>
       <c r="U445" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.79; 일치키워드=24v가,open; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.79; 일치키워드=24v가,open; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -47216,7 +47216,7 @@
       </c>
       <c r="U446" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.79; 일치키워드=24v가,open,상태가; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.79; 일치키워드=24v가,open,상태가; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -47323,7 +47323,7 @@
       </c>
       <c r="U447" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.79; 일치키워드=24v가,open,되고; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.79; 일치키워드=24v가,open,되고; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -47430,7 +47430,7 @@
       </c>
       <c r="U448" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.79; 일치키워드=24v가,open,비활성화; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.79; 일치키워드=24v가,open,비활성화; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -47537,7 +47537,7 @@
       </c>
       <c r="U449" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.79; 일치키워드=24v가,open,비활성화; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.79; 일치키워드=24v가,open,비활성화; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -47644,7 +47644,7 @@
       </c>
       <c r="U450" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.79; 일치키워드=24v가,open,되고; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.79; 일치키워드=24v가,open,되고; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -47751,7 +47751,7 @@
       </c>
       <c r="U451" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.79; 일치키워드=24v가,open,비활성화; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.79; 일치키워드=24v가,open,비활성화; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -47854,7 +47854,7 @@
       </c>
       <c r="U452" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.81; 일치키워드=10v,20ma,모드,전류,전압; 텍스트순위=2; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.81; 일치키워드=10v,20ma,모드,전류,전압; 텍스트순위=2; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -47957,7 +47957,7 @@
       </c>
       <c r="U453" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.77; 일치키워드=모드,전류,전압; 텍스트순위=2; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.77; 일치키워드=모드,전류,전압; 텍스트순위=2; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -48060,7 +48060,7 @@
       </c>
       <c r="U454" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.91; 일치키워드=10v,20ma,모드,전류,전압; 텍스트순위=2; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.91; 일치키워드=10v,20ma,모드,전류,전압; 텍스트순위=2; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -48167,7 +48167,7 @@
       </c>
       <c r="U455" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.80; 일치키워드=10v,20ma,모드,전류,전압; 텍스트순위=2; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.80; 일치키워드=10v,20ma,모드,전류,전압; 텍스트순위=2; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -48274,7 +48274,7 @@
       </c>
       <c r="U456" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.77; 일치키워드=모드,전류,전압; 텍스트순위=2; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.77; 일치키워드=모드,전류,전압; 텍스트순위=2; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -48381,7 +48381,7 @@
       </c>
       <c r="U457" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.97; 일치키워드=10v,20ma,모드,전류,전압; 텍스트순위=2; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.97; 일치키워드=10v,20ma,모드,전류,전압; 텍스트순위=2; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -48488,7 +48488,7 @@
       </c>
       <c r="U458" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.84; 일치키워드=10v,20ma,모드,전류,전압; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.84; 일치키워드=10v,20ma,모드,전류,전압; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -48595,7 +48595,7 @@
       </c>
       <c r="U459" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.92; 일치키워드=10v,20ma,모드,전류,전압; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.92; 일치키워드=10v,20ma,모드,전류,전압; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -48702,7 +48702,7 @@
       </c>
       <c r="U460" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.91; 일치키워드=10v,20ma,모드,전류,전압; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.91; 일치키워드=10v,20ma,모드,전류,전압; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -48805,7 +48805,7 @@
       </c>
       <c r="U461" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.78; 의미유사도=0.76; 일치키워드=라이트,매트,비상정지,스위치,안전,연결할,커튼; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.78; 의미유사도=0.76; 일치키워드=라이트,매트,비상정지,스위치,안전,연결할,커튼; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -48908,7 +48908,7 @@
       </c>
       <c r="U462" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.56; 의미유사도=0.87; 일치키워드=라이트,비상정지,스위치,안전,커튼; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.56; 의미유사도=0.87; 일치키워드=라이트,비상정지,스위치,안전,커튼; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -49011,7 +49011,7 @@
       </c>
       <c r="U463" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.90; 일치키워드=라이트,매트,비상정지,스위치,안전,커튼; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.90; 일치키워드=라이트,매트,비상정지,스위치,안전,커튼; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -49118,7 +49118,7 @@
       </c>
       <c r="U464" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.78; 의미유사도=0.75; 일치키워드=라이트,매트,비상정지,스위치,안전,연결할,커튼; 텍스트순위=1; 이미지순위=3</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.78; 의미유사도=0.75; 일치키워드=라이트,매트,비상정지,스위치,안전,연결할,커튼; 텍스트순위=1; 이미지순위=3</t>
         </is>
       </c>
     </row>
@@ -49225,7 +49225,7 @@
       </c>
       <c r="U465" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.79; 일치키워드=라이트,비상정지,스위치,안전,연결할,커튼; 텍스트순위=1; 이미지순위=3</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.79; 일치키워드=라이트,비상정지,스위치,안전,연결할,커튼; 텍스트순위=1; 이미지순위=3</t>
         </is>
       </c>
     </row>
@@ -49332,7 +49332,7 @@
       </c>
       <c r="U466" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.90; 일치키워드=라이트,매트,비상정지,스위치,안전,커튼; 텍스트순위=1; 이미지순위=3</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.90; 일치키워드=라이트,매트,비상정지,스위치,안전,커튼; 텍스트순위=1; 이미지순위=3</t>
         </is>
       </c>
     </row>
@@ -49439,7 +49439,7 @@
       </c>
       <c r="U467" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.78; 의미유사도=0.75; 일치키워드=라이트,매트,비상정지,스위치,안전,연결할,커튼; 텍스트순위=1; 이미지순위=3</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.78; 의미유사도=0.75; 일치키워드=라이트,매트,비상정지,스위치,안전,연결할,커튼; 텍스트순위=1; 이미지순위=3</t>
         </is>
       </c>
     </row>
@@ -49546,7 +49546,7 @@
       </c>
       <c r="U468" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.56; 의미유사도=0.87; 일치키워드=라이트,비상정지,스위치,안전,커튼; 텍스트순위=1; 이미지순위=3</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.56; 의미유사도=0.87; 일치키워드=라이트,비상정지,스위치,안전,커튼; 텍스트순위=1; 이미지순위=3</t>
         </is>
       </c>
     </row>
@@ -49653,7 +49653,7 @@
       </c>
       <c r="U469" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.90; 일치키워드=라이트,매트,비상정지,스위치,안전,커튼; 텍스트순위=1; 이미지순위=3</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.90; 일치키워드=라이트,매트,비상정지,스위치,안전,커튼; 텍스트순위=1; 이미지순위=3</t>
         </is>
       </c>
     </row>
@@ -49756,7 +49756,7 @@
       </c>
       <c r="U470" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.63; 일치키워드=입력받을; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.63; 일치키워드=입력받을; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -49859,7 +49859,7 @@
       </c>
       <c r="U471" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.69; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.69; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -49962,7 +49962,7 @@
       </c>
       <c r="U472" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.78; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.78; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -50069,7 +50069,7 @@
       </c>
       <c r="U473" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.67; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.67; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -50176,7 +50176,7 @@
       </c>
       <c r="U474" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.73; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.73; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -50283,7 +50283,7 @@
       </c>
       <c r="U475" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.69; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.69; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -50390,7 +50390,7 @@
       </c>
       <c r="U476" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.69; 일치키워드=입력받을; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.69; 일치키워드=입력받을; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -50497,7 +50497,7 @@
       </c>
       <c r="U477" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.69; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.69; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -50604,7 +50604,7 @@
       </c>
       <c r="U478" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.78; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.78; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -50707,7 +50707,7 @@
       </c>
       <c r="U479" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.78; 일치키워드=16개와,디지털; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.78; 일치키워드=16개와,디지털; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -50810,7 +50810,7 @@
       </c>
       <c r="U480" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.85; 일치키워드=디지털; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.85; 일치키워드=디지털; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -50913,7 +50913,7 @@
       </c>
       <c r="U481" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.70; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.70; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -51020,7 +51020,7 @@
       </c>
       <c r="U482" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.78; 일치키워드=16개와,디지털; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.78; 일치키워드=16개와,디지털; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -51127,7 +51127,7 @@
       </c>
       <c r="U483" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.85; 일치키워드=16개와,디지털; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.85; 일치키워드=16개와,디지털; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -51234,7 +51234,7 @@
       </c>
       <c r="U484" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.70; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.70; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -51341,7 +51341,7 @@
       </c>
       <c r="U485" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.78; 일치키워드=16개와,디지털; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.78; 일치키워드=16개와,디지털; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -51448,7 +51448,7 @@
       </c>
       <c r="U486" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.85; 일치키워드=디지털; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.85; 일치키워드=디지털; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -51555,7 +51555,7 @@
       </c>
       <c r="U487" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.78; 일치키워드=디지털; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.78; 일치키워드=디지털; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -51658,7 +51658,7 @@
       </c>
       <c r="U488" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.85; 일치키워드=gio,oxx,단자,단자와,부하를,사이에; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.85; 일치키워드=gio,oxx,단자,단자와,부하를,사이에; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -51761,7 +51761,7 @@
       </c>
       <c r="U489" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.78; 의미유사도=0.95; 일치키워드=gio,oxx,tbco1,단자,단자와,부하를,사이에; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.78; 의미유사도=0.95; 일치키워드=gio,oxx,tbco1,단자,단자와,부하를,사이에; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -51864,7 +51864,7 @@
       </c>
       <c r="U490" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.78; 의미유사도=0.86; 일치키워드=gio,oxx,tbco1,단자,단자와,부하를,사이에; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.78; 의미유사도=0.86; 일치키워드=gio,oxx,tbco1,단자,단자와,부하를,사이에; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -51971,7 +51971,7 @@
       </c>
       <c r="U491" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.77; 일치키워드=gio,oxx,단자,단자와,부하를,사이에; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.77; 일치키워드=gio,oxx,단자,단자와,부하를,사이에; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -52078,7 +52078,7 @@
       </c>
       <c r="U492" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.78; 의미유사도=0.95; 일치키워드=gio,oxx,tbco1,단자,단자와,부하를,사이에; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.78; 의미유사도=0.95; 일치키워드=gio,oxx,tbco1,단자,단자와,부하를,사이에; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -52185,7 +52185,7 @@
       </c>
       <c r="U493" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.78; 의미유사도=0.96; 일치키워드=gio,oxx,tbco1,단자,단자와,부하를,사이에; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.78; 의미유사도=0.96; 일치키워드=gio,oxx,tbco1,단자,단자와,부하를,사이에; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -52292,7 +52292,7 @@
       </c>
       <c r="U494" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.85; 일치키워드=gio,oxx,단자,단자와,부하를,사이에; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.85; 일치키워드=gio,oxx,단자,단자와,부하를,사이에; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -52399,7 +52399,7 @@
       </c>
       <c r="U495" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.78; 의미유사도=0.96; 일치키워드=gio,oxx,tbco1,단자,단자와,부하를,사이에; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.78; 의미유사도=0.96; 일치키워드=gio,oxx,tbco1,단자,단자와,부하를,사이에; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -52506,7 +52506,7 @@
       </c>
       <c r="U496" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.78; 의미유사도=0.86; 일치키워드=gio,oxx,tbco1,단자,단자와,부하를,사이에; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.78; 의미유사도=0.86; 일치키워드=gio,oxx,tbco1,단자,단자와,부하를,사이에; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -52609,7 +52609,7 @@
       </c>
       <c r="U497" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.43; 의미유사도=0.77; 일치키워드=negative,외부기기의,입력단자에; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.43; 의미유사도=0.77; 일치키워드=negative,외부기기의,입력단자에; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -52712,7 +52712,7 @@
       </c>
       <c r="U498" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.29; 의미유사도=0.80; 일치키워드=negative,외부기기의; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.29; 의미유사도=0.80; 일치키워드=negative,외부기기의; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -52815,7 +52815,7 @@
       </c>
       <c r="U499" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.77; 일치키워드=negative; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.77; 일치키워드=negative; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -52922,7 +52922,7 @@
       </c>
       <c r="U500" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.43; 의미유사도=0.78; 일치키워드=negative,외부기기의,입력단자에; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.43; 의미유사도=0.78; 일치키워드=negative,외부기기의,입력단자에; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -53029,7 +53029,7 @@
       </c>
       <c r="U501" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.43; 의미유사도=0.80; 일치키워드=negative,외부기기의,입력단자에; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.43; 의미유사도=0.80; 일치키워드=negative,외부기기의,입력단자에; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -53136,7 +53136,7 @@
       </c>
       <c r="U502" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.29; 의미유사도=0.77; 일치키워드=negative,외부기기의; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.29; 의미유사도=0.77; 일치키워드=negative,외부기기의; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -53243,7 +53243,7 @@
       </c>
       <c r="U503" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.43; 의미유사도=0.77; 일치키워드=negative,외부기기의,입력단자에; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.43; 의미유사도=0.77; 일치키워드=negative,외부기기의,입력단자에; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -53350,7 +53350,7 @@
       </c>
       <c r="U504" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.43; 의미유사도=0.80; 일치키워드=negative,외부기기의,입력단자에; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.43; 의미유사도=0.80; 일치키워드=negative,외부기기의,입력단자에; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -53457,7 +53457,7 @@
       </c>
       <c r="U505" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.29; 의미유사도=0.77; 일치키워드=negative,외부기기의; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.29; 의미유사도=0.77; 일치키워드=negative,외부기기의; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -53560,7 +53560,7 @@
       </c>
       <c r="U506" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.49; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.49; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -53663,7 +53663,7 @@
       </c>
       <c r="U507" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.80; 의미유사도=0.66; 일치키워드=si1,si2,si3,si4; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.80; 의미유사도=0.66; 일치키워드=si1,si2,si3,si4; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -53766,7 +53766,7 @@
       </c>
       <c r="U508" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.64; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.64; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -53873,7 +53873,7 @@
       </c>
       <c r="U509" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.50; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.50; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -53980,7 +53980,7 @@
       </c>
       <c r="U510" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.74; 일치키워드=si1,si2,si3,si4,단자; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.74; 일치키워드=si1,si2,si3,si4,단자; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -54087,7 +54087,7 @@
       </c>
       <c r="U511" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.60; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.60; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -54194,7 +54194,7 @@
       </c>
       <c r="U512" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.50; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.50; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -54301,7 +54301,7 @@
       </c>
       <c r="U513" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.80; 의미유사도=0.66; 일치키워드=si1,si2,si3,si4; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.80; 의미유사도=0.66; 일치키워드=si1,si2,si3,si4; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -54408,7 +54408,7 @@
       </c>
       <c r="U514" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.59; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.59; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -54511,7 +54511,7 @@
       </c>
       <c r="U515" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.45; 의미유사도=0.85; 일치키워드=ip,modbus,tcp,외부,인터넷; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.45; 의미유사도=0.85; 일치키워드=ip,modbus,tcp,외부,인터넷; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -54614,7 +54614,7 @@
       </c>
       <c r="U516" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.36; 의미유사도=0.90; 일치키워드=ip,modbus,tcp,외부; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.36; 의미유사도=0.90; 일치키워드=ip,modbus,tcp,외부; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -54717,7 +54717,7 @@
       </c>
       <c r="U517" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.55; 의미유사도=0.89; 일치키워드=ip,modbus,tcp,연결,외부,인터넷; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.55; 의미유사도=0.89; 일치키워드=ip,modbus,tcp,연결,외부,인터넷; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -54824,7 +54824,7 @@
       </c>
       <c r="U518" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.45; 의미유사도=0.84; 일치키워드=ip,modbus,tcp,외부,인터넷; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.45; 의미유사도=0.84; 일치키워드=ip,modbus,tcp,외부,인터넷; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -54931,7 +54931,7 @@
       </c>
       <c r="U519" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.27; 의미유사도=0.91; 일치키워드=modbus,tcp,외부; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.27; 의미유사도=0.91; 일치키워드=modbus,tcp,외부; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -55038,7 +55038,7 @@
       </c>
       <c r="U520" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.55; 의미유사도=0.88; 일치키워드=ip,modbus,tcp,연결,외부,인터넷; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.55; 의미유사도=0.88; 일치키워드=ip,modbus,tcp,연결,외부,인터넷; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -55145,7 +55145,7 @@
       </c>
       <c r="U521" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.45; 의미유사도=0.84; 일치키워드=ip,modbus,tcp,외부,인터넷; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.45; 의미유사도=0.84; 일치키워드=ip,modbus,tcp,외부,인터넷; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -55252,7 +55252,7 @@
       </c>
       <c r="U522" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.27; 의미유사도=0.91; 일치키워드=modbus,tcp,외부; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.27; 의미유사도=0.91; 일치키워드=modbus,tcp,외부; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -55359,7 +55359,7 @@
       </c>
       <c r="U523" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.55; 의미유사도=0.89; 일치키워드=ip,modbus,tcp,연결,외부,인터넷; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.55; 의미유사도=0.89; 일치키워드=ip,modbus,tcp,연결,외부,인터넷; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -55462,7 +55462,7 @@
       </c>
       <c r="U524" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.75; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.75; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -55565,7 +55565,7 @@
       </c>
       <c r="U525" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.79; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.79; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -55668,7 +55668,7 @@
       </c>
       <c r="U526" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.29; 의미유사도=0.80; 일치키워드=x축,y축; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.29; 의미유사도=0.80; 일치키워드=x축,y축; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -55775,7 +55775,7 @@
       </c>
       <c r="U527" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.78; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.78; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -55882,7 +55882,7 @@
       </c>
       <c r="U528" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.81; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.81; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -55989,7 +55989,7 @@
       </c>
       <c r="U529" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.29; 의미유사도=0.80; 일치키워드=x축,y축; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.29; 의미유사도=0.80; 일치키워드=x축,y축; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -56099,7 +56099,7 @@
       </c>
       <c r="U530" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.29; 의미유사도=0.78; 일치키워드=x축,y축; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.29; 의미유사도=0.78; 일치키워드=x축,y축; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -56206,7 +56206,7 @@
       </c>
       <c r="U531" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.81; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.81; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -56313,7 +56313,7 @@
       </c>
       <c r="U532" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.29; 의미유사도=0.80; 일치키워드=x축,y축; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.29; 의미유사도=0.80; 일치키워드=x축,y축; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -56416,7 +56416,7 @@
       </c>
       <c r="U533" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.80; 의미유사도=0.75; 일치키워드=로봇을,발생하거나,설정할,안전,오류가,운반,위반이,지속되는; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.80; 의미유사도=0.75; 일치키워드=로봇을,발생하거나,설정할,안전,오류가,운반,위반이,지속되는; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -56519,7 +56519,7 @@
       </c>
       <c r="U534" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.70; 의미유사도=0.81; 일치키워드=로봇을,발생하거나,설정할,안전,오류가,위반이,지속되는; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.70; 의미유사도=0.81; 일치키워드=로봇을,발생하거나,설정할,안전,오류가,위반이,지속되는; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -56622,7 +56622,7 @@
       </c>
       <c r="U535" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.80; 의미유사도=0.82; 일치키워드=로봇을,발생하거나,설정할,안전,오류가,운반,위반이,지속되는; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.80; 의미유사도=0.82; 일치키워드=로봇을,발생하거나,설정할,안전,오류가,운반,위반이,지속되는; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -56729,7 +56729,7 @@
       </c>
       <c r="U536" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.80; 의미유사도=0.76; 일치키워드=로봇을,발생하거나,설정할,안전,오류가,운반,위반이,지속되는; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.80; 의미유사도=0.76; 일치키워드=로봇을,발생하거나,설정할,안전,오류가,운반,위반이,지속되는; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -56836,7 +56836,7 @@
       </c>
       <c r="U537" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.70; 의미유사도=0.81; 일치키워드=로봇을,발생하거나,설정할,안전,오류가,위반이,지속되는; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.70; 의미유사도=0.81; 일치키워드=로봇을,발생하거나,설정할,안전,오류가,위반이,지속되는; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -56943,7 +56943,7 @@
       </c>
       <c r="U538" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.80; 의미유사도=0.82; 일치키워드=로봇을,발생하거나,설정할,안전,오류가,운반,위반이,지속되는; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.80; 의미유사도=0.82; 일치키워드=로봇을,발생하거나,설정할,안전,오류가,운반,위반이,지속되는; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -57050,7 +57050,7 @@
       </c>
       <c r="U539" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.80; 의미유사도=0.76; 일치키워드=로봇을,발생하거나,설정할,안전,오류가,운반,위반이,지속되는; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.80; 의미유사도=0.76; 일치키워드=로봇을,발생하거나,설정할,안전,오류가,운반,위반이,지속되는; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -57157,7 +57157,7 @@
       </c>
       <c r="U540" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.70; 의미유사도=0.81; 일치키워드=로봇을,발생하거나,설정할,안전,오류가,위반이,지속되는; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.70; 의미유사도=0.81; 일치키워드=로봇을,발생하거나,설정할,안전,오류가,위반이,지속되는; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -57264,7 +57264,7 @@
       </c>
       <c r="U541" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.80; 의미유사도=0.82; 일치키워드=로봇을,발생하거나,설정할,안전,오류가,운반,위반이,지속되는; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.80; 의미유사도=0.82; 일치키워드=로봇을,발생하거나,설정할,안전,오류가,운반,위반이,지속되는; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -57367,7 +57367,7 @@
       </c>
       <c r="U542" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.78; 의미유사도=0.71; 일치키워드=기존,내보내기,불러오기,생성,수행할,저장,파일; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.78; 의미유사도=0.71; 일치키워드=기존,내보내기,불러오기,생성,수행할,저장,파일; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -57470,7 +57470,7 @@
       </c>
       <c r="U543" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.44; 의미유사도=0.79; 일치키워드=내보내기,등을,저장,파일; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.44; 의미유사도=0.79; 일치키워드=내보내기,등을,저장,파일; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -57573,7 +57573,7 @@
       </c>
       <c r="U544" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.68; 일치키워드=내보내기,등을,불러오기; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.68; 일치키워드=내보내기,등을,불러오기; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -57680,7 +57680,7 @@
       </c>
       <c r="U545" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.78; 의미유사도=0.71; 일치키워드=기존,내보내기,불러오기,생성,수행할,저장,파일; 텍스트순위=1; 이미지순위=5</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.78; 의미유사도=0.71; 일치키워드=기존,내보내기,불러오기,생성,수행할,저장,파일; 텍스트순위=1; 이미지순위=5</t>
         </is>
       </c>
     </row>
@@ -57787,7 +57787,7 @@
       </c>
       <c r="U546" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.44; 의미유사도=0.79; 일치키워드=내보내기,등을,저장,파일; 텍스트순위=1; 이미지순위=5</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.44; 의미유사도=0.79; 일치키워드=내보내기,등을,저장,파일; 텍스트순위=1; 이미지순위=5</t>
         </is>
       </c>
     </row>
@@ -57894,7 +57894,7 @@
       </c>
       <c r="U547" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.68; 일치키워드=내보내기,등을,불러오기; 텍스트순위=1; 이미지순위=5</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.68; 일치키워드=내보내기,등을,불러오기; 텍스트순위=1; 이미지순위=5</t>
         </is>
       </c>
     </row>
@@ -58001,7 +58001,7 @@
       </c>
       <c r="U548" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.78; 의미유사도=0.71; 일치키워드=기존,내보내기,불러오기,생성,수행할,저장,파일; 텍스트순위=1; 이미지순위=5</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.78; 의미유사도=0.71; 일치키워드=기존,내보내기,불러오기,생성,수행할,저장,파일; 텍스트순위=1; 이미지순위=5</t>
         </is>
       </c>
     </row>
@@ -58108,7 +58108,7 @@
       </c>
       <c r="U549" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.44; 의미유사도=0.79; 일치키워드=내보내기,등을,저장,파일; 텍스트순위=1; 이미지순위=5</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.44; 의미유사도=0.79; 일치키워드=내보내기,등을,저장,파일; 텍스트순위=1; 이미지순위=5</t>
         </is>
       </c>
     </row>
@@ -58215,7 +58215,7 @@
       </c>
       <c r="U550" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.77; 일치키워드=내보내기,등을,파일; 텍스트순위=1; 이미지순위=5</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.77; 일치키워드=내보내기,등을,파일; 텍스트순위=1; 이미지순위=5</t>
         </is>
       </c>
     </row>
@@ -58318,7 +58318,7 @@
       </c>
       <c r="U551" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.76; 일치키워드=기능을,버튼; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.76; 일치키워드=기능을,버튼; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -58421,7 +58421,7 @@
       </c>
       <c r="U552" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.76; 일치키워드=버튼; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.76; 일치키워드=버튼; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -58524,7 +58524,7 @@
       </c>
       <c r="U553" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.83; 일치키워드=버튼; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.83; 일치키워드=버튼; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -58631,7 +58631,7 @@
       </c>
       <c r="U554" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.76; 일치키워드=기능을,버튼; 텍스트순위=1; 이미지순위=7</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.76; 일치키워드=기능을,버튼; 텍스트순위=1; 이미지순위=7</t>
         </is>
       </c>
     </row>
@@ -58738,7 +58738,7 @@
       </c>
       <c r="U555" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.76; 일치키워드=버튼; 텍스트순위=1; 이미지순위=7</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.76; 일치키워드=버튼; 텍스트순위=1; 이미지순위=7</t>
         </is>
       </c>
     </row>
@@ -58845,7 +58845,7 @@
       </c>
       <c r="U556" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.83; 일치키워드=버튼; 텍스트순위=1; 이미지순위=7</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.83; 일치키워드=버튼; 텍스트순위=1; 이미지순위=7</t>
         </is>
       </c>
     </row>
@@ -58952,7 +58952,7 @@
       </c>
       <c r="U557" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.76; 일치키워드=기능을,버튼; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.76; 일치키워드=기능을,버튼; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -59059,7 +59059,7 @@
       </c>
       <c r="U558" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.77; 일치키워드=버튼; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.77; 일치키워드=버튼; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -59166,7 +59166,7 @@
       </c>
       <c r="U559" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.83; 일치키워드=버튼; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.83; 일치키워드=버튼; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -59271,7 +59271,7 @@
       </c>
       <c r="U560" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.81; 일치키워드=parameters,robot,settings,tool,weight; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.81; 일치키워드=parameters,robot,settings,tool,weight; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -59374,7 +59374,7 @@
       </c>
       <c r="U561" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=1.00; 일치키워드=parameters,robot,settings,tool,weight; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=1.00; 일치키워드=parameters,robot,settings,tool,weight; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -59477,7 +59477,7 @@
       </c>
       <c r="U562" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=1.00; 일치키워드=parameters,robot,settings,tool,weight; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=1.00; 일치키워드=parameters,robot,settings,tool,weight; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -59586,7 +59586,7 @@
       </c>
       <c r="U563" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.81; 일치키워드=parameters,robot,settings,tool,weight; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.81; 일치키워드=parameters,robot,settings,tool,weight; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -59693,7 +59693,7 @@
       </c>
       <c r="U564" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=1.00; 일치키워드=parameters,robot,settings,tool,weight; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=1.00; 일치키워드=parameters,robot,settings,tool,weight; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -59800,7 +59800,7 @@
       </c>
       <c r="U565" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=1.00; 일치키워드=parameters,robot,settings,tool,weight; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=1.00; 일치키워드=parameters,robot,settings,tool,weight; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -59908,7 +59908,7 @@
       </c>
       <c r="U566" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.84; 일치키워드=parameters,robot,settings,tool,weight; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.84; 일치키워드=parameters,robot,settings,tool,weight; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -60015,7 +60015,7 @@
       </c>
       <c r="U567" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=1.00; 일치키워드=parameters,robot,settings,tool,weight; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=1.00; 일치키워드=parameters,robot,settings,tool,weight; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -60122,7 +60122,7 @@
       </c>
       <c r="U568" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.91; 일치키워드=parameters,robot,settings,tool,weight; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.91; 일치키워드=parameters,robot,settings,tool,weight; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -60228,7 +60228,7 @@
       </c>
       <c r="U569" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.73; 일치키워드=shape의,tool,이름을,입력해야; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.73; 일치키워드=shape의,tool,이름을,입력해야; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -60331,7 +60331,7 @@
       </c>
       <c r="U570" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.84; 일치키워드=tool,이름을,입력해야; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.84; 일치키워드=tool,이름을,입력해야; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -60434,7 +60434,7 @@
       </c>
       <c r="U571" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.84; 일치키워드=이름을,입력해야; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.84; 일치키워드=이름을,입력해야; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -60544,7 +60544,7 @@
       </c>
       <c r="U572" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.73; 일치키워드=shape의,tool,이름을,입력해야; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.73; 일치키워드=shape의,tool,이름을,입력해야; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -60651,7 +60651,7 @@
       </c>
       <c r="U573" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.80; 일치키워드=tool,입력해야; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.80; 일치키워드=tool,입력해야; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -60758,7 +60758,7 @@
       </c>
       <c r="U574" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.84; 일치키워드=tool,이름을,입력해야; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.84; 일치키워드=tool,이름을,입력해야; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -60868,7 +60868,7 @@
       </c>
       <c r="U575" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.73; 일치키워드=shape의,tool,이름을,입력해야; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.73; 일치키워드=shape의,tool,이름을,입력해야; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -60975,7 +60975,7 @@
       </c>
       <c r="U576" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.92; 일치키워드=tool,이름을,입력해야; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.92; 일치키워드=tool,이름을,입력해야; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -61082,7 +61082,7 @@
       </c>
       <c r="U577" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.78; 일치키워드=tool,이름을,입력해야; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.75; 의미유사도=0.78; 일치키워드=tool,이름을,입력해야; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
     </row>
@@ -61185,7 +61185,7 @@
       </c>
       <c r="U578" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.65; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.65; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -61288,7 +61288,7 @@
       </c>
       <c r="U579" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.55; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.55; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -61391,7 +61391,7 @@
       </c>
       <c r="U580" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.84; 일치키워드=값을; 텍스트순위=3; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.84; 일치키워드=값을; 텍스트순위=3; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -61494,7 +61494,7 @@
       </c>
       <c r="U581" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.65; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.65; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -61598,7 +61598,7 @@
       </c>
       <c r="U582" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.59; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.59; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -61701,7 +61701,7 @@
       </c>
       <c r="U583" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.46; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.46; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -61804,7 +61804,7 @@
       </c>
       <c r="U584" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.64; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.64; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -61908,7 +61908,7 @@
       </c>
       <c r="U585" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.65; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.65; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -62011,7 +62011,7 @@
       </c>
       <c r="U586" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.69; 일치키워드=값을; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.69; 일치키워드=값을; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -62124,7 +62124,7 @@
       </c>
       <c r="U587" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.54; 일치키워드=; 텍스트순위=4; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.54; 일치키워드=; 텍스트순위=4; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -62228,7 +62228,7 @@
       </c>
       <c r="U588" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.47; 일치키워드=; 텍스트순위=4; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.47; 일치키워드=; 텍스트순위=4; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -62331,7 +62331,7 @@
       </c>
       <c r="U589" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.56; 일치키워드=; 텍스트순위=4; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.56; 일치키워드=; 텍스트순위=4; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -62448,7 +62448,7 @@
       </c>
       <c r="U590" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.58; 일치키워드=; 텍스트순위=4; 이미지순위=4</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.58; 일치키워드=; 텍스트순위=4; 이미지순위=4</t>
         </is>
       </c>
     </row>
@@ -62556,7 +62556,7 @@
       </c>
       <c r="U591" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.48; 일치키워드=; 텍스트순위=4; 이미지순위=4</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.48; 일치키워드=; 텍스트순위=4; 이미지순위=4</t>
         </is>
       </c>
     </row>
@@ -62663,7 +62663,7 @@
       </c>
       <c r="U592" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.53; 일치키워드=; 텍스트순위=4; 이미지순위=4</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.53; 일치키워드=; 텍스트순위=4; 이미지순위=4</t>
         </is>
       </c>
     </row>
@@ -62780,7 +62780,7 @@
       </c>
       <c r="U593" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.56; 일치키워드=; 텍스트순위=4; 이미지순위=4</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.56; 일치키워드=; 텍스트순위=4; 이미지순위=4</t>
         </is>
       </c>
     </row>
@@ -62888,7 +62888,7 @@
       </c>
       <c r="U594" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.48; 일치키워드=; 텍스트순위=4; 이미지순위=4</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.48; 일치키워드=; 텍스트순위=4; 이미지순위=4</t>
         </is>
       </c>
     </row>
@@ -62995,7 +62995,7 @@
       </c>
       <c r="U595" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.53; 일치키워드=; 텍스트순위=4; 이미지순위=4</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.53; 일치키워드=; 텍스트순위=4; 이미지순위=4</t>
         </is>
       </c>
     </row>
@@ -63098,7 +63098,7 @@
       </c>
       <c r="U596" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.30; 의미유사도=0.71; 일치키워드=감지,민감도를,충돌; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.30; 의미유사도=0.71; 일치키워드=감지,민감도를,충돌; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -63201,7 +63201,7 @@
       </c>
       <c r="U597" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.69; 일치키워드=감지,충돌; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.69; 일치키워드=감지,충돌; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -63304,7 +63304,7 @@
       </c>
       <c r="U598" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.10; 의미유사도=0.69; 일치키워드=충돌; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.10; 의미유사도=0.69; 일치키워드=충돌; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -63411,7 +63411,7 @@
       </c>
       <c r="U599" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.30; 의미유사도=0.71; 일치키워드=감지,민감도를,충돌; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.30; 의미유사도=0.71; 일치키워드=감지,민감도를,충돌; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -63518,7 +63518,7 @@
       </c>
       <c r="U600" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.69; 일치키워드=감지,충돌; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.69; 일치키워드=감지,충돌; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -63625,7 +63625,7 @@
       </c>
       <c r="U601" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.10; 의미유사도=0.69; 일치키워드=충돌; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.10; 의미유사도=0.69; 일치키워드=충돌; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -63732,7 +63732,7 @@
       </c>
       <c r="U602" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.69; 일치키워드=감지,충돌; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.69; 일치키워드=감지,충돌; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -63839,7 +63839,7 @@
       </c>
       <c r="U603" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.70; 일치키워드=감지,충돌; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.70; 일치키워드=감지,충돌; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -63946,7 +63946,7 @@
       </c>
       <c r="U604" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.10; 의미유사도=0.69; 일치키워드=충돌; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.10; 의미유사도=0.69; 일치키워드=충돌; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -64049,7 +64049,7 @@
       </c>
       <c r="U605" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.74; 일치키워드=parameter,robot,값이,데이터,변경된; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.74; 일치키워드=parameter,robot,값이,데이터,변경된; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -64152,7 +64152,7 @@
       </c>
       <c r="U606" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.74; 일치키워드=parameter,robot,값이,데이터,변경된; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.74; 일치키워드=parameter,robot,값이,데이터,변경된; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -64255,7 +64255,7 @@
       </c>
       <c r="U607" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.43; 의미유사도=0.71; 일치키워드=값이,데이터,변경된; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.43; 의미유사도=0.71; 일치키워드=값이,데이터,변경된; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -64362,7 +64362,7 @@
       </c>
       <c r="U608" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.74; 일치키워드=parameter,robot,값이,데이터,변경된; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.74; 일치키워드=parameter,robot,값이,데이터,변경된; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -64469,7 +64469,7 @@
       </c>
       <c r="U609" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.74; 일치키워드=parameter,robot,값이,데이터,변경된; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.74; 일치키워드=parameter,robot,값이,데이터,변경된; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -64576,7 +64576,7 @@
       </c>
       <c r="U610" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.43; 의미유사도=0.70; 일치키워드=값이,데이터,변경된; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.43; 의미유사도=0.70; 일치키워드=값이,데이터,변경된; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -64683,7 +64683,7 @@
       </c>
       <c r="U611" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.74; 일치키워드=parameter,robot,값이,데이터,변경된; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.74; 일치키워드=parameter,robot,값이,데이터,변경된; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -64790,7 +64790,7 @@
       </c>
       <c r="U612" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.74; 일치키워드=parameter,robot,값이,데이터,변경된; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.71; 의미유사도=0.74; 일치키워드=parameter,robot,값이,데이터,변경된; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -64897,7 +64897,7 @@
       </c>
       <c r="U613" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.43; 의미유사도=0.71; 일치키워드=값이,데이터,변경된; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.43; 의미유사도=0.71; 일치키워드=값이,데이터,변경된; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -65003,7 +65003,7 @@
       </c>
       <c r="U614" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.66; 일치키워드=모듈,설정하고,설정해야,신호를,안전,태스크를; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.66; 일치키워드=모듈,설정하고,설정해야,신호를,안전,태스크를; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -65106,7 +65106,7 @@
       </c>
       <c r="U615" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.85; 일치키워드=설정해야,신호를,안전,태스크를; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.85; 일치키워드=설정해야,신호를,안전,태스크를; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -65212,7 +65212,7 @@
       </c>
       <c r="U616" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.65; 일치키워드=모듈,설정해야,신호를,안전,태스크를; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.65; 일치키워드=모듈,설정해야,신호를,안전,태스크를; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -65322,7 +65322,7 @@
       </c>
       <c r="U617" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.66; 일치키워드=모듈,설정해야,신호를,안전,태스크를; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.66; 일치키워드=모듈,설정해야,신호를,안전,태스크를; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -65429,7 +65429,7 @@
       </c>
       <c r="U618" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.85; 일치키워드=설정해야,신호를,안전,태스크를; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.85; 일치키워드=설정해야,신호를,안전,태스크를; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -65539,7 +65539,7 @@
       </c>
       <c r="U619" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.65; 일치키워드=모듈,설정해야,신호를,안전,태스크를; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.83; 의미유사도=0.65; 일치키워드=모듈,설정해야,신호를,안전,태스크를; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -65649,7 +65649,7 @@
       </c>
       <c r="U620" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.66; 일치키워드=모듈,설정하고,설정해야,신호를,안전,태스크를; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.66; 일치키워드=모듈,설정하고,설정해야,신호를,안전,태스크를; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -65756,7 +65756,7 @@
       </c>
       <c r="U621" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.85; 일치키워드=설정해야,신호를,안전,태스크를; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.85; 일치키워드=설정해야,신호를,안전,태스크를; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -65866,7 +65866,7 @@
       </c>
       <c r="U622" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.65; 일치키워드=모듈,신호를,안전,태스크를; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.67; 의미유사도=0.65; 일치키워드=모듈,신호를,안전,태스크를; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -65969,7 +65969,7 @@
       </c>
       <c r="U623" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.78; 일치키워드=high,low,회색으로; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.78; 일치키워드=high,low,회색으로; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -66072,7 +66072,7 @@
       </c>
       <c r="U624" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.81; 일치키워드=high,low,회색으로; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.81; 일치키워드=high,low,회색으로; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -66175,7 +66175,7 @@
       </c>
       <c r="U625" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.76; 일치키워드=high,low,회색으로; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.76; 일치키워드=high,low,회색으로; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
     </row>
@@ -66282,7 +66282,7 @@
       </c>
       <c r="U626" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.78; 일치키워드=high,low,회색으로; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.78; 일치키워드=high,low,회색으로; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -66389,7 +66389,7 @@
       </c>
       <c r="U627" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.81; 일치키워드=high,low,회색으로; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.81; 일치키워드=high,low,회색으로; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -66496,7 +66496,7 @@
       </c>
       <c r="U628" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.76; 일치키워드=high,low,회색으로; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.76; 일치키워드=high,low,회색으로; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -66603,7 +66603,7 @@
       </c>
       <c r="U629" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.78; 일치키워드=high,low,회색으로; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.78; 일치키워드=high,low,회색으로; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -66710,7 +66710,7 @@
       </c>
       <c r="U630" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.81; 일치키워드=high,low,회색으로; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.81; 일치키워드=high,low,회색으로; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
@@ -66817,7 +66817,7 @@
       </c>
       <c r="U631" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.76; 일치키워드=high,low,회색으로; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.76; 일치키워드=high,low,회색으로; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
     </row>
